--- a/templates/Timiron_Operations_Dashboard_MASTER.xlsx
+++ b/templates/Timiron_Operations_Dashboard_MASTER.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operations Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mar 2026 P&amp;L Forecast" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mar 2026 Weekly" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apr 2026 P&amp;L Forecast" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apr 2026 Weekly" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Headcount &amp; Roster" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pump Runtime" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maintenance Calendar" sheetId="6" state="visible" r:id="rId6"/>
@@ -23,7 +23,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="12">
+  <numFmts count="21">
     <numFmt numFmtId="164" formatCode="\$#,##0_);[RED]&quot;($&quot;#,##0\)"/>
     <numFmt numFmtId="165" formatCode="#,##0_);[RED]\(#,##0\)"/>
     <numFmt numFmtId="166" formatCode="#,##0.00_);[RED]\(#,##0.00\)"/>
@@ -36,8 +36,17 @@
     <numFmt numFmtId="173" formatCode="&quot;~$&quot;#,##0.00"/>
     <numFmt numFmtId="174" formatCode="\$#,##0.0000"/>
     <numFmt numFmtId="175" formatCode="0.000"/>
+    <numFmt numFmtId="176" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="177" formatCode="0.0"/>
+    <numFmt numFmtId="178" formatCode="0.0000"/>
+    <numFmt numFmtId="179" formatCode="$#,##0_);[RED]&quot;($&quot;#,##0\)"/>
+    <numFmt numFmtId="180" formatCode="0,##0.00"/>
+    <numFmt numFmtId="181" formatCode="\$#,##0_);[Red]&quot;($&quot;#,##0\)"/>
+    <numFmt numFmtId="182" formatCode="\$#,##0.00_);[Red]&quot;($&quot;#,##0.00\)"/>
+    <numFmt numFmtId="183" formatCode="$#,##0.000"/>
+    <numFmt numFmtId="184" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="94">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -339,8 +348,313 @@
       <color rgb="FF7F6000"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font/>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="002F5496"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="002F5496"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF333333"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFE74C3C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFC00000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF888888"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF7F6000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF7F6000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFC00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FFC00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF375623"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF375623"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF375623"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF806000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF806000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00806000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <i val="1"/>
+      <color rgb="FF666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF9C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF006100"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <i val="1"/>
+      <color rgb="FF595959"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <color rgb="FF333333"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <b val="1"/>
+      <color rgb="FF333333"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <color rgb="FF333333"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001A3A5C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00806000"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="30">
+  <fills count="45">
     <fill>
       <patternFill/>
     </fill>
@@ -515,8 +829,83 @@
         <bgColor rgb="FF7F6000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F5496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A3A5C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A3A5C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -611,6 +1000,253 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
+    <border>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="001A3A5C"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="medium">
+        <color rgb="001A3A5C"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB0B0B0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB0B0B0"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB0B0B0"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB0B0B0"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -622,7 +1258,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="546">
+  <cellXfs count="811">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2255,6 +2891,717 @@
     <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="31" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="48" fillId="32" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="48" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="48" fillId="33" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="49" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="48" fillId="32" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="48" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="48" fillId="33" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="49" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="48" fillId="32" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="48" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="48" fillId="33" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="49" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="48" fillId="32" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="48" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="48" fillId="33" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="49" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="31" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="33" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="33" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="177" fontId="48" fillId="33" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="49" fillId="33" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="48" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="49" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="33" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="177" fontId="49" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="48" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="48" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="48" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="48" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="32" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="49" fillId="32" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="51" fillId="32" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="33" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="49" fillId="33" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="51" fillId="33" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="51" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="53" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="54" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="55" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="53" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="53" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="53" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="55" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="57" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="58" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="59" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="60" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="59" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="61" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="62" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="60" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="61" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="62" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="63" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="62" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="65" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="66" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="65" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="65" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="65" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="64" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="34" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="34" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="65" fillId="34" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="64" fillId="34" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="59" fillId="34" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="65" fillId="34" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="65" fillId="34" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="65" fillId="34" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="64" fillId="34" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="64" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="59" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="63" fillId="34" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="65" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="63" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="64" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="64" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="64" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="65" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="65" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="67" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="65" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="65" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="65" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="34" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="65" fillId="34" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="65" fillId="34" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="60" fillId="34" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="65" fillId="34" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="65" fillId="34" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="65" fillId="34" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="60" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="61" fillId="34" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="61" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="64" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="64" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="64" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="64" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="64" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="35" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="69" fillId="36" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="65" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="43" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="70" fillId="37" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="65" fillId="34" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="51" fillId="38" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="64" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="35" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="65" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="69" fillId="36" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="65" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="65" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="65" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="34" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="65" fillId="34" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="70" fillId="37" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="65" fillId="34" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="65" fillId="34" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="65" fillId="34" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="51" fillId="38" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="64" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="64" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="64" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="64" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="14"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="68" fillId="39" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="74" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="66" fillId="40" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="74" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="74" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="74" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="74" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="73" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="74" fillId="41" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="74" fillId="41" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="75" fillId="42" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="74" fillId="41" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="74" fillId="41" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="74" fillId="41" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="74" fillId="41" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="74" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="66" fillId="40" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="74" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="74" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="74" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="74" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="76" fillId="43" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="41" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="74" fillId="41" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="76" fillId="43" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="74" fillId="41" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="74" fillId="41" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="74" fillId="41" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="74" fillId="41" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="77" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="77" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="77" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="77" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="77" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="2" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="79" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="182" fontId="80" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="182" fontId="80" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="81" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="182" fontId="81" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="182" fontId="81" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="82" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="81" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="83" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="80" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="80" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="79" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="87" fillId="44" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="89" fillId="35" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="177" fontId="65" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="64" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="177" fontId="64" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="64" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="183" fontId="64" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="184" fontId="64" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="184" fontId="64" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="184" fontId="65" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="32" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="65" fillId="32" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="65" fillId="32" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="32" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="64" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="64" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2504,823 +3851,841 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:R19"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.71484375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" style="272" min="1" max="1"/>
-    <col width="9" customWidth="1" style="272" min="2" max="2"/>
-    <col width="12" customWidth="1" style="272" min="3" max="6"/>
-    <col width="9" customWidth="1" style="272" min="7" max="15"/>
-    <col width="15" customWidth="1" style="272" min="16" max="17"/>
-    <col width="17" customWidth="1" style="272" min="18" max="18"/>
+    <col width="12.85546875" customWidth="1" style="273" min="1" max="1"/>
+    <col width="8" customWidth="1" style="273" min="2" max="2"/>
+    <col width="12" customWidth="1" style="273" min="3" max="3"/>
+    <col width="13" customWidth="1" style="273" min="4" max="4"/>
+    <col width="13" customWidth="1" style="273" min="5" max="5"/>
+    <col width="10" customWidth="1" style="273" min="6" max="6"/>
+    <col width="8" customWidth="1" style="273" min="7" max="7"/>
+    <col width="13" customWidth="1" style="273" min="8" max="8"/>
+    <col width="13" customWidth="1" style="273" min="9" max="9"/>
+    <col width="10" customWidth="1" style="273" min="10" max="10"/>
+    <col width="13" customWidth="1" style="273" min="11" max="11"/>
+    <col width="13" customWidth="1" style="273" min="12" max="12"/>
+    <col width="13" customWidth="1" style="273" min="13" max="13"/>
+    <col width="13" customWidth="1" style="273" min="14" max="14"/>
+    <col width="13" customWidth="1" style="273" min="15" max="15"/>
+    <col width="2" customWidth="1" style="273" min="16" max="16"/>
+    <col width="13" customWidth="1" style="273" min="17" max="17"/>
+    <col width="17" customWidth="1" style="273" min="18" max="18"/>
+    <col width="13" customWidth="1" style="273" min="19" max="19"/>
+    <col width="13" customWidth="1" style="273" min="20" max="20"/>
+    <col width="13" customWidth="1" style="273" min="21" max="21"/>
+    <col width="13" customWidth="1" style="273" min="22" max="22"/>
+    <col width="13" customWidth="1" style="273" min="23" max="23"/>
+    <col width="13" customWidth="1" style="273" min="24" max="24"/>
+    <col width="13" customWidth="1" style="273" min="25" max="25"/>
+    <col width="13" customWidth="1" style="273" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="273">
-      <c r="A1" s="274" t="inlineStr">
-        <is>
-          <t>|  OPERATIONS &amp; FINANCIAL DASHBOARD  (Apr 2025 – Mar 2026)</t>
+      <c r="A1" s="708" t="inlineStr">
+        <is>
+          <t>|  OPERATIONS &amp; FINANCIAL DASHBOARD  (May 2025 – Apr 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="6" customHeight="1" s="273"/>
     <row r="3" ht="13.5" customHeight="1" s="273">
-      <c r="A3" s="275" t="inlineStr">
-        <is>
-          <t>Source: Actual P&amp;Ls, Master Load Logs, Payroll Files, Trafigura Invoices  |  Forecast: Mar 2026 based on 30-day actuals (through Mar 30)  |  Mar 2026 costs from Mar P&amp;L Forecast tab</t>
+      <c r="A3" s="709" t="inlineStr">
+        <is>
+          <t>Source: Actual P&amp;Ls, Master Load Logs, Payroll Files, Trafigura Invoices  |  †Apr 2026 = Forecast  |  †Mar 2026 = Final Forecast (31 days)  |  Dec 2025 cost negative due to $71k payroll reversal</t>
         </is>
       </c>
     </row>
     <row r="4" ht="39.75" customHeight="1" s="273">
-      <c r="A4" s="276" t="inlineStr">
+      <c r="A4" s="710" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B4" s="276" t="inlineStr">
-        <is>
-          <t>Headcount</t>
-        </is>
-      </c>
-      <c r="C4" s="276" t="inlineStr">
+      <c r="B4" s="710" t="inlineStr">
+        <is>
+          <t>Head-
+count</t>
+        </is>
+      </c>
+      <c r="C4" s="710" t="inlineStr">
         <is>
           <t>Operating
 Revenue ($)</t>
         </is>
       </c>
-      <c r="D4" s="276" t="inlineStr">
+      <c r="D4" s="710" t="inlineStr">
         <is>
           <t>Operating
 Cost ($)</t>
         </is>
       </c>
-      <c r="E4" s="276" t="inlineStr">
-        <is>
-          <t>EBITDA ($)</t>
-        </is>
-      </c>
-      <c r="F4" s="276" t="inlineStr">
+      <c r="E4" s="710" t="inlineStr">
         <is>
           <t>Net
 Income ($)</t>
         </is>
       </c>
-      <c r="G4" s="276" t="inlineStr">
+      <c r="F4" s="710" t="inlineStr">
         <is>
           <t>Total
 Barrels</t>
         </is>
       </c>
-      <c r="H4" s="276" t="inlineStr">
+      <c r="G4" s="710" t="inlineStr">
         <is>
           <t>Bbls /
 Day</t>
         </is>
       </c>
-      <c r="I4" s="276" t="inlineStr">
+      <c r="H4" s="710" t="inlineStr">
         <is>
           <t>Trucks /
 Day</t>
         </is>
       </c>
-      <c r="J4" s="276" t="inlineStr">
+      <c r="I4" s="710" t="inlineStr">
         <is>
           <t>Total
 Trucks</t>
         </is>
       </c>
-      <c r="K4" s="276" t="inlineStr">
+      <c r="J4" s="710" t="inlineStr">
         <is>
           <t>Revenue /
 Bbl ($)</t>
         </is>
       </c>
-      <c r="L4" s="276" t="inlineStr">
+      <c r="K4" s="710" t="inlineStr">
         <is>
           <t>Cost /
 Bbl ($)</t>
         </is>
       </c>
-      <c r="M4" s="276" t="inlineStr">
-        <is>
-          <t>EBITDA /
+      <c r="L4" s="710" t="inlineStr">
+        <is>
+          <t>Net /
 Bbl ($)</t>
         </is>
       </c>
-      <c r="N4" s="277" t="inlineStr">
+      <c r="M4" s="710" t="inlineStr">
         <is>
           <t>Adj Pump
 Util %*</t>
         </is>
       </c>
-      <c r="O4" s="277" t="inlineStr">
-        <is>
-          <t>Rail
-Cap / Day**</t>
-        </is>
-      </c>
-      <c r="P4" s="278" t="n"/>
+      <c r="N4" s="710" t="inlineStr">
+        <is>
+          <t>Rail Cap /
+Day**</t>
+        </is>
+      </c>
+      <c r="O4" s="710" t="inlineStr">
+        <is>
+          <t>Net /
+Head ($)</t>
+        </is>
+      </c>
+      <c r="P4" s="711" t="n"/>
     </row>
     <row r="5" ht="15.75" customHeight="1" s="273">
-      <c r="A5" s="279" t="inlineStr">
-        <is>
-          <t>Apr 2025</t>
-        </is>
-      </c>
-      <c r="B5" s="280" t="n">
+      <c r="A5" s="712" t="inlineStr">
+        <is>
+          <t>May 2025</t>
+        </is>
+      </c>
+      <c r="B5" s="713" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="281" t="n">
-        <v>84059.48</v>
-      </c>
-      <c r="D5" s="281" t="n">
-        <v>169781.48</v>
-      </c>
-      <c r="E5" s="282" t="n">
-        <v>-86145.86</v>
-      </c>
-      <c r="F5" s="283" t="n">
-        <v>-86145.86</v>
-      </c>
-      <c r="G5" s="284" t="n">
-        <v>36041</v>
-      </c>
-      <c r="H5" s="284" t="n">
-        <v>1201</v>
-      </c>
-      <c r="I5" s="285" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J5" s="284" t="n">
-        <v>184</v>
-      </c>
-      <c r="K5" s="286" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="L5" s="286" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="M5" s="286" t="n">
-        <v>-2.39</v>
-      </c>
-      <c r="N5" s="287" t="inlineStr">
+      <c r="C5" s="713" t="n">
+        <v>85594.5</v>
+      </c>
+      <c r="D5" s="713" t="n">
+        <v>76686.72</v>
+      </c>
+      <c r="E5" s="714" t="n">
+        <v>7950.54</v>
+      </c>
+      <c r="F5" s="713" t="n">
+        <v>95027</v>
+      </c>
+      <c r="G5" s="713" t="n">
+        <v>3066</v>
+      </c>
+      <c r="H5" s="715" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="I5" s="713" t="n">
+        <v>485</v>
+      </c>
+      <c r="J5" s="716" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K5" s="716" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L5" s="716" t="n">
+        <v>0.0836661159459943</v>
+      </c>
+      <c r="M5" s="717" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="N5" s="717" t="n">
+        <v>0.2044</v>
+      </c>
+      <c r="O5" s="718" t="n">
+        <v>1988</v>
+      </c>
+      <c r="P5" s="719" t="n"/>
+    </row>
+    <row r="6" ht="15.75" customHeight="1" s="273">
+      <c r="A6" s="720" t="inlineStr">
+        <is>
+          <t>Jun 2025</t>
+        </is>
+      </c>
+      <c r="B6" s="721" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" s="721" t="n">
+        <v>141001.36</v>
+      </c>
+      <c r="D6" s="721" t="n">
+        <v>163036.53</v>
+      </c>
+      <c r="E6" s="722" t="n">
+        <v>-23345.8</v>
+      </c>
+      <c r="F6" s="721" t="n">
+        <v>141709</v>
+      </c>
+      <c r="G6" s="721" t="n">
+        <v>4724</v>
+      </c>
+      <c r="H6" s="723" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I6" s="721" t="n">
+        <v>723</v>
+      </c>
+      <c r="J6" s="724" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="724" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L6" s="724" t="n">
+        <v>-0.1647446527743474</v>
+      </c>
+      <c r="M6" s="725" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O5" s="288" t="n">
-        <v>0.0800666666666667</v>
-      </c>
-      <c r="P5" s="278" t="n"/>
-    </row>
-    <row r="6" ht="15.75" customHeight="1" s="273">
-      <c r="A6" s="289" t="inlineStr">
-        <is>
-          <t>May 2025</t>
-        </is>
-      </c>
-      <c r="B6" s="290" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" s="291" t="n">
-        <v>85594.5</v>
-      </c>
-      <c r="D6" s="291" t="n">
-        <v>76686.72</v>
-      </c>
-      <c r="E6" s="291" t="n">
-        <v>7950.54</v>
-      </c>
-      <c r="F6" s="292" t="n">
-        <v>7950.54</v>
-      </c>
-      <c r="G6" s="293" t="n">
-        <v>95027</v>
-      </c>
-      <c r="H6" s="293" t="n">
-        <v>3066</v>
-      </c>
-      <c r="I6" s="294" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="J6" s="293" t="n">
-        <v>485</v>
-      </c>
-      <c r="K6" s="295" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L6" s="295" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="M6" s="295" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="N6" s="288" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="O6" s="288" t="n">
-        <v>0.2044</v>
-      </c>
-      <c r="P6" s="278" t="n"/>
+      <c r="N6" s="725" t="n">
+        <v>0.314933333333333</v>
+      </c>
+      <c r="O6" s="726" t="n">
+        <v>-3891</v>
+      </c>
+      <c r="P6" s="719" t="n"/>
     </row>
     <row r="7" ht="15.75" customHeight="1" s="273">
-      <c r="A7" s="279" t="inlineStr">
-        <is>
-          <t>Jun 2025</t>
-        </is>
-      </c>
-      <c r="B7" s="280" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7" s="281" t="n">
-        <v>141001.36</v>
-      </c>
-      <c r="D7" s="281" t="n">
-        <v>163036.53</v>
-      </c>
-      <c r="E7" s="282" t="n">
-        <v>-23345.8</v>
-      </c>
-      <c r="F7" s="283" t="n">
-        <v>-23345.8</v>
-      </c>
-      <c r="G7" s="284" t="n">
-        <v>141709</v>
-      </c>
-      <c r="H7" s="284" t="n">
-        <v>4724</v>
-      </c>
-      <c r="I7" s="285" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="J7" s="284" t="n">
-        <v>723</v>
-      </c>
-      <c r="K7" s="286" t="n">
+      <c r="A7" s="727" t="inlineStr">
+        <is>
+          <t>Jul 2025</t>
+        </is>
+      </c>
+      <c r="B7" s="728" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" s="728" t="n">
+        <v>233009.82</v>
+      </c>
+      <c r="D7" s="728" t="n">
+        <v>207679.45</v>
+      </c>
+      <c r="E7" s="729" t="n">
+        <v>22968.16</v>
+      </c>
+      <c r="F7" s="728" t="n">
+        <v>169856</v>
+      </c>
+      <c r="G7" s="728" t="n">
+        <v>5479</v>
+      </c>
+      <c r="H7" s="730" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I7" s="728" t="n">
+        <v>866</v>
+      </c>
+      <c r="J7" s="731" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="K7" s="731" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L7" s="731" t="n">
+        <v>0.1352213639788998</v>
+      </c>
+      <c r="M7" s="732" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="N7" s="732" t="n">
+        <v>0.365266666666667</v>
+      </c>
+      <c r="O7" s="733" t="n">
+        <v>2871</v>
+      </c>
+      <c r="P7" s="719" t="n"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1" s="273">
+      <c r="A8" s="720" t="inlineStr">
+        <is>
+          <t>Aug 2025</t>
+        </is>
+      </c>
+      <c r="B8" s="721" t="n">
+        <v>10</v>
+      </c>
+      <c r="C8" s="721" t="n">
+        <v>284021.38</v>
+      </c>
+      <c r="D8" s="721" t="n">
+        <v>299476.01</v>
+      </c>
+      <c r="E8" s="722" t="n">
+        <v>-20414.92</v>
+      </c>
+      <c r="F8" s="721" t="n">
+        <v>292714</v>
+      </c>
+      <c r="G8" s="721" t="n">
+        <v>9443</v>
+      </c>
+      <c r="H8" s="723" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="I8" s="721" t="n">
+        <v>1493</v>
+      </c>
+      <c r="J8" s="724" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="K8" s="724" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L8" s="724" t="n">
+        <v>-0.0697435722240822</v>
+      </c>
+      <c r="M8" s="725" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="N8" s="725" t="n">
+        <v>0.6295333333333329</v>
+      </c>
+      <c r="O8" s="726" t="n">
+        <v>-2041</v>
+      </c>
+      <c r="P8" s="719" t="n"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="273">
+      <c r="A9" s="727" t="inlineStr">
+        <is>
+          <t>Sep 2025</t>
+        </is>
+      </c>
+      <c r="B9" s="728" t="n">
+        <v>12</v>
+      </c>
+      <c r="C9" s="728" t="n">
+        <v>345382.18</v>
+      </c>
+      <c r="D9" s="728" t="n">
+        <v>314889.15</v>
+      </c>
+      <c r="E9" s="729" t="n">
+        <v>19707.8</v>
+      </c>
+      <c r="F9" s="728" t="n">
+        <v>241480</v>
+      </c>
+      <c r="G9" s="728" t="n">
+        <v>8049</v>
+      </c>
+      <c r="H9" s="730" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="I9" s="728" t="n">
+        <v>1232</v>
+      </c>
+      <c r="J9" s="731" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="K9" s="731" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L9" s="731" t="n">
+        <v>0.08161255590525095</v>
+      </c>
+      <c r="M9" s="732" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="N9" s="732" t="n">
+        <v>0.5366</v>
+      </c>
+      <c r="O9" s="733" t="n">
+        <v>1642</v>
+      </c>
+      <c r="P9" s="719" t="n"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1" s="273">
+      <c r="A10" s="720" t="inlineStr">
+        <is>
+          <t>Oct 2025</t>
+        </is>
+      </c>
+      <c r="B10" s="721" t="n">
+        <v>12</v>
+      </c>
+      <c r="C10" s="721" t="n">
+        <v>231889.91</v>
+      </c>
+      <c r="D10" s="721" t="n">
+        <v>435995.82</v>
+      </c>
+      <c r="E10" s="722" t="n">
+        <v>-205270.59</v>
+      </c>
+      <c r="F10" s="721" t="n">
+        <v>220569</v>
+      </c>
+      <c r="G10" s="721" t="n">
+        <v>7115</v>
+      </c>
+      <c r="H10" s="723" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="I10" s="721" t="n">
+        <v>1125</v>
+      </c>
+      <c r="J10" s="724" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="K10" s="724" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="L10" s="724" t="n">
+        <v>-0.9306411599091441</v>
+      </c>
+      <c r="M10" s="725" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="N10" s="725" t="n">
+        <v>0.474333333333333</v>
+      </c>
+      <c r="O10" s="726" t="n">
+        <v>-17106</v>
+      </c>
+      <c r="P10" s="719" t="n"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1" s="273">
+      <c r="A11" s="727" t="inlineStr">
+        <is>
+          <t>Nov 2025</t>
+        </is>
+      </c>
+      <c r="B11" s="728" t="n">
+        <v>12</v>
+      </c>
+      <c r="C11" s="728" t="n">
+        <v>219082.57</v>
+      </c>
+      <c r="D11" s="728" t="n">
+        <v>274936.26</v>
+      </c>
+      <c r="E11" s="722" t="n">
+        <v>-61267.29</v>
+      </c>
+      <c r="F11" s="728" t="n">
+        <v>176502</v>
+      </c>
+      <c r="G11" s="728" t="n">
+        <v>5883</v>
+      </c>
+      <c r="H11" s="730" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="I11" s="728" t="n">
+        <v>901</v>
+      </c>
+      <c r="J11" s="731" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="K11" s="731" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="L11" s="731" t="n">
+        <v>-0.3471195227249549</v>
+      </c>
+      <c r="M11" s="732" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="N11" s="732" t="n">
+        <v>0.3922</v>
+      </c>
+      <c r="O11" s="733" t="n">
+        <v>-5106</v>
+      </c>
+      <c r="P11" s="719" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="273">
+      <c r="A12" s="720" t="inlineStr">
+        <is>
+          <t>Dec 2025</t>
+        </is>
+      </c>
+      <c r="B12" s="721" t="n">
+        <v>12</v>
+      </c>
+      <c r="C12" s="721" t="n">
+        <v>265411.9</v>
+      </c>
+      <c r="D12" s="721" t="n">
+        <v>-150595.85</v>
+      </c>
+      <c r="E12" s="734" t="n">
+        <v>299307.88</v>
+      </c>
+      <c r="F12" s="721" t="n">
+        <v>195816</v>
+      </c>
+      <c r="G12" s="721" t="n">
+        <v>6317</v>
+      </c>
+      <c r="H12" s="723" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="I12" s="721" t="n">
+        <v>999</v>
+      </c>
+      <c r="J12" s="724" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="K12" s="724" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="L12" s="724" t="n">
+        <v>1.528515953752502</v>
+      </c>
+      <c r="M12" s="725" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="N12" s="725" t="n">
+        <v>0.421133333333333</v>
+      </c>
+      <c r="O12" s="726" t="n">
+        <v>24942</v>
+      </c>
+      <c r="P12" s="719" t="n"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" s="273">
+      <c r="A13" s="727" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+      <c r="B13" s="728" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" s="728" t="n">
+        <v>307918.66</v>
+      </c>
+      <c r="D13" s="728" t="n">
+        <v>310402.29</v>
+      </c>
+      <c r="E13" s="722" t="n">
+        <v>-5171.48</v>
+      </c>
+      <c r="F13" s="728" t="n">
+        <v>308000</v>
+      </c>
+      <c r="G13" s="728" t="n">
+        <v>9936</v>
+      </c>
+      <c r="H13" s="730" t="n">
+        <v>32</v>
+      </c>
+      <c r="I13" s="728" t="n">
+        <v>1571</v>
+      </c>
+      <c r="J13" s="731" t="n">
         <v>1</v>
       </c>
-      <c r="L7" s="286" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="M7" s="286" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="N7" s="287" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O7" s="288" t="n">
-        <v>0.314933333333333</v>
-      </c>
-      <c r="P7" s="278" t="n"/>
-    </row>
-    <row r="8" ht="15.75" customHeight="1" s="273">
-      <c r="A8" s="289" t="inlineStr">
-        <is>
-          <t>Jul 2025</t>
-        </is>
-      </c>
-      <c r="B8" s="290" t="n">
-        <v>8</v>
-      </c>
-      <c r="C8" s="291" t="n">
-        <v>233009.82</v>
-      </c>
-      <c r="D8" s="291" t="n">
-        <v>207679.45</v>
-      </c>
-      <c r="E8" s="291" t="n">
-        <v>22968.16</v>
-      </c>
-      <c r="F8" s="292" t="n">
-        <v>22968.16</v>
-      </c>
-      <c r="G8" s="293" t="n">
-        <v>169856</v>
-      </c>
-      <c r="H8" s="293" t="n">
-        <v>5479</v>
-      </c>
-      <c r="I8" s="294" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="J8" s="293" t="n">
-        <v>866</v>
-      </c>
-      <c r="K8" s="295" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="L8" s="295" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="M8" s="295" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="N8" s="288" t="n">
-        <v>0.271</v>
-      </c>
-      <c r="O8" s="288" t="n">
-        <v>0.365266666666667</v>
-      </c>
-      <c r="P8" s="278" t="n"/>
-    </row>
-    <row r="9" ht="15.75" customHeight="1" s="273">
-      <c r="A9" s="279" t="inlineStr">
-        <is>
-          <t>Aug 2025</t>
-        </is>
-      </c>
-      <c r="B9" s="280" t="n">
-        <v>10</v>
-      </c>
-      <c r="C9" s="281" t="n">
-        <v>284021.38</v>
-      </c>
-      <c r="D9" s="281" t="n">
-        <v>299476.01</v>
-      </c>
-      <c r="E9" s="281" t="n">
-        <v>-20414.92</v>
-      </c>
-      <c r="F9" s="283" t="n">
-        <v>-20414.92</v>
-      </c>
-      <c r="G9" s="284" t="n">
-        <v>292714</v>
-      </c>
-      <c r="H9" s="284" t="n">
-        <v>9443</v>
-      </c>
-      <c r="I9" s="285" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="J9" s="284" t="n">
-        <v>1493</v>
-      </c>
-      <c r="K9" s="286" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="L9" s="286" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="M9" s="286" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="N9" s="296" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="O9" s="296" t="n">
-        <v>0.6295333333333329</v>
-      </c>
-      <c r="P9" s="278" t="n"/>
-    </row>
-    <row r="10" ht="15.75" customHeight="1" s="273">
-      <c r="A10" s="289" t="inlineStr">
-        <is>
-          <t>Sep 2025</t>
-        </is>
-      </c>
-      <c r="B10" s="290" t="n">
-        <v>12</v>
-      </c>
-      <c r="C10" s="291" t="n">
-        <v>345382.18</v>
-      </c>
-      <c r="D10" s="291" t="n">
-        <v>314889.15</v>
-      </c>
-      <c r="E10" s="291" t="n">
-        <v>19707.8</v>
-      </c>
-      <c r="F10" s="292" t="n">
-        <v>19707.8</v>
-      </c>
-      <c r="G10" s="293" t="n">
-        <v>241480</v>
-      </c>
-      <c r="H10" s="293" t="n">
-        <v>8049</v>
-      </c>
-      <c r="I10" s="294" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="J10" s="293" t="n">
-        <v>1232</v>
-      </c>
-      <c r="K10" s="295" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="L10" s="295" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M10" s="295" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="N10" s="296" t="n">
-        <v>0.458</v>
-      </c>
-      <c r="O10" s="296" t="n">
-        <v>0.5366</v>
-      </c>
-      <c r="P10" s="278" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" s="273">
-      <c r="A11" s="279" t="inlineStr">
-        <is>
-          <t>Oct 2025</t>
-        </is>
-      </c>
-      <c r="B11" s="280" t="n">
-        <v>12</v>
-      </c>
-      <c r="C11" s="281" t="n">
-        <v>231889.91</v>
-      </c>
-      <c r="D11" s="281" t="n">
-        <v>435995.82</v>
-      </c>
-      <c r="E11" s="282" t="n">
-        <v>-205270.59</v>
-      </c>
-      <c r="F11" s="283" t="n">
-        <v>-205270.59</v>
-      </c>
-      <c r="G11" s="284" t="n">
-        <v>220569</v>
-      </c>
-      <c r="H11" s="284" t="n">
-        <v>7115</v>
-      </c>
-      <c r="I11" s="285" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="J11" s="284" t="n">
-        <v>1125</v>
-      </c>
-      <c r="K11" s="286" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="L11" s="286" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="M11" s="286" t="n">
-        <v>-0.93</v>
-      </c>
-      <c r="N11" s="288" t="n">
-        <v>0.397</v>
-      </c>
-      <c r="O11" s="288" t="n">
-        <v>0.474333333333333</v>
-      </c>
-      <c r="P11" s="278" t="n"/>
-    </row>
-    <row r="12" ht="15.75" customHeight="1" s="273">
-      <c r="A12" s="289" t="inlineStr">
-        <is>
-          <t>Nov 2025</t>
-        </is>
-      </c>
-      <c r="B12" s="290" t="n">
-        <v>12</v>
-      </c>
-      <c r="C12" s="291" t="n">
-        <v>219082.57</v>
-      </c>
-      <c r="D12" s="291" t="n">
-        <v>274936.26</v>
-      </c>
-      <c r="E12" s="297" t="n">
-        <v>-61267.29</v>
-      </c>
-      <c r="F12" s="283" t="n">
-        <v>-61267.29</v>
-      </c>
-      <c r="G12" s="293" t="n">
-        <v>176502</v>
-      </c>
-      <c r="H12" s="293" t="n">
-        <v>5883</v>
-      </c>
-      <c r="I12" s="294" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="J12" s="293" t="n">
-        <v>901</v>
-      </c>
-      <c r="K12" s="295" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="L12" s="295" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="M12" s="295" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="N12" s="288" t="n">
-        <v>0.329</v>
-      </c>
-      <c r="O12" s="288" t="n">
-        <v>0.3922</v>
-      </c>
-      <c r="P12" s="278" t="n"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1" s="273">
-      <c r="A13" s="279" t="inlineStr">
-        <is>
-          <t>Dec 2025</t>
-        </is>
-      </c>
-      <c r="B13" s="280" t="n">
-        <v>12</v>
-      </c>
-      <c r="C13" s="281" t="n">
-        <v>265411.9</v>
-      </c>
-      <c r="D13" s="281" t="n">
-        <v>-150595.85</v>
-      </c>
-      <c r="E13" s="281" t="n">
-        <v>299307.88</v>
-      </c>
-      <c r="F13" s="292" t="n">
-        <v>299307.88</v>
-      </c>
-      <c r="G13" s="284" t="n">
-        <v>195816</v>
-      </c>
-      <c r="H13" s="284" t="n">
-        <v>6317</v>
-      </c>
-      <c r="I13" s="285" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="J13" s="284" t="n">
-        <v>999</v>
-      </c>
-      <c r="K13" s="286" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="L13" s="286" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="M13" s="286" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="N13" s="288" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="O13" s="288" t="n">
-        <v>0.421133333333333</v>
-      </c>
-      <c r="P13" s="278" t="n"/>
+      <c r="K13" s="731" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L13" s="731" t="n">
+        <v>-0.01679051948051948</v>
+      </c>
+      <c r="M13" s="732" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="N13" s="732" t="n">
+        <v>0.6624</v>
+      </c>
+      <c r="O13" s="733" t="n">
+        <v>-431</v>
+      </c>
+      <c r="P13" s="719" t="n"/>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="273">
-      <c r="A14" s="289" t="inlineStr">
-        <is>
-          <t>Jan 2026</t>
-        </is>
-      </c>
-      <c r="B14" s="290" t="n">
-        <v>12</v>
-      </c>
-      <c r="C14" s="291" t="n">
-        <v>307918.66</v>
-      </c>
-      <c r="D14" s="291" t="n">
-        <v>310402.29</v>
-      </c>
-      <c r="E14" s="291" t="n">
-        <v>-5171.48</v>
-      </c>
-      <c r="F14" s="283" t="n">
-        <v>-5171.48</v>
-      </c>
-      <c r="G14" s="293" t="n">
-        <v>308000</v>
-      </c>
-      <c r="H14" s="293" t="n">
-        <v>9936</v>
-      </c>
-      <c r="I14" s="294" t="n">
-        <v>32</v>
-      </c>
-      <c r="J14" s="293" t="n">
-        <v>1571</v>
-      </c>
-      <c r="K14" s="295" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" s="295" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M14" s="295" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="N14" s="288" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="O14" s="296" t="n">
-        <v>0.6624</v>
-      </c>
-      <c r="P14" s="278" t="n"/>
+      <c r="A14" s="720" t="inlineStr">
+        <is>
+          <t>Feb 2026</t>
+        </is>
+      </c>
+      <c r="B14" s="721" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" s="721" t="n">
+        <v>344761.32</v>
+      </c>
+      <c r="D14" s="721" t="n">
+        <v>234498.18</v>
+      </c>
+      <c r="E14" s="734" t="n">
+        <v>102949.81</v>
+      </c>
+      <c r="F14" s="721" t="n">
+        <v>313600</v>
+      </c>
+      <c r="G14" s="721" t="n">
+        <v>11200</v>
+      </c>
+      <c r="H14" s="723" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="I14" s="721" t="n">
+        <v>1600</v>
+      </c>
+      <c r="J14" s="724" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K14" s="724" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L14" s="724" t="n">
+        <v>0.3282838329081633</v>
+      </c>
+      <c r="M14" s="725" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="N14" s="725" t="n">
+        <v>0.746666666666667</v>
+      </c>
+      <c r="O14" s="726" t="n">
+        <v>7919</v>
+      </c>
+      <c r="P14" s="719" t="n"/>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="273">
-      <c r="A15" s="279" t="inlineStr">
-        <is>
-          <t>Feb 2026</t>
-        </is>
-      </c>
-      <c r="B15" s="280" t="n">
-        <v>13</v>
-      </c>
-      <c r="C15" s="281" t="n">
-        <v>344761.32</v>
-      </c>
-      <c r="D15" s="281" t="n">
-        <v>234498.18</v>
-      </c>
-      <c r="E15" s="281" t="n">
-        <v>102949.81</v>
-      </c>
-      <c r="F15" s="292" t="n">
-        <v>102949.81</v>
-      </c>
-      <c r="G15" s="284" t="n">
-        <v>313600</v>
-      </c>
-      <c r="H15" s="284" t="n">
-        <v>11200</v>
-      </c>
-      <c r="I15" s="285" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="J15" s="284" t="n">
+      <c r="A15" s="727" t="inlineStr">
+        <is>
+          <t>Mar 2026†</t>
+        </is>
+      </c>
+      <c r="B15" s="728" t="n">
+        <v>15</v>
+      </c>
+      <c r="C15" s="728" t="n">
+        <v>356011.03</v>
+      </c>
+      <c r="D15" s="728" t="n">
+        <v>244583.52</v>
+      </c>
+      <c r="E15" s="734" t="n">
+        <v>111427.51</v>
+      </c>
+      <c r="F15" s="728" t="n">
+        <v>319681</v>
+      </c>
+      <c r="G15" s="728" t="n">
+        <v>10312.3</v>
+      </c>
+      <c r="H15" s="730" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="I15" s="728" t="n">
         <v>1600</v>
       </c>
-      <c r="K15" s="286" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L15" s="286" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="M15" s="286" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="N15" s="296" t="n">
-        <v>0.439</v>
-      </c>
-      <c r="O15" s="296" t="n">
-        <v>0.746666666666667</v>
-      </c>
-      <c r="P15" s="278" t="n"/>
+      <c r="J15" s="731" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K15" s="731" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="L15" s="731" t="n">
+        <v>0.3485584379428243</v>
+      </c>
+      <c r="M15" s="732" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="N15" s="732" t="n">
+        <v>0.687487</v>
+      </c>
+      <c r="O15" s="733" t="n">
+        <v>7429</v>
+      </c>
+      <c r="P15" s="719" t="n"/>
     </row>
     <row r="16" ht="15.75" customHeight="1" s="273">
-      <c r="A16" s="298" t="inlineStr">
-        <is>
-          <t>Mar 2026†</t>
-        </is>
-      </c>
-      <c r="B16" s="299" t="n">
-        <v>14</v>
-      </c>
-      <c r="C16" s="300" t="n">
-        <v>356011.03</v>
-      </c>
-      <c r="D16" s="301" t="n">
-        <v>244583.52</v>
-      </c>
-      <c r="E16" s="301" t="n">
-        <v>111427.51</v>
-      </c>
-      <c r="F16" s="302" t="n">
-        <v>111427.51</v>
-      </c>
-      <c r="G16" s="303" t="n">
-        <v>319681</v>
-      </c>
-      <c r="H16" s="303" t="n">
-        <v>10312.3</v>
-      </c>
-      <c r="I16" s="304" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="J16" s="303" t="n">
-        <v>1600</v>
-      </c>
-      <c r="K16" s="305" t="n">
+      <c r="A16" s="735" t="inlineStr">
+        <is>
+          <t>April 2026†</t>
+        </is>
+      </c>
+      <c r="B16" s="736" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" s="736" t="n">
+        <v>407307</v>
+      </c>
+      <c r="D16" s="736" t="n">
+        <v>255376</v>
+      </c>
+      <c r="E16" s="737" t="n">
+        <v>151931</v>
+      </c>
+      <c r="F16" s="736" t="n">
+        <v>368079</v>
+      </c>
+      <c r="G16" s="736" t="n">
+        <v>12269</v>
+      </c>
+      <c r="H16" s="738" t="n">
+        <v>61</v>
+      </c>
+      <c r="I16" s="736" t="n">
+        <v>1830</v>
+      </c>
+      <c r="J16" s="739" t="n">
         <v>1.11</v>
       </c>
-      <c r="L16" s="305" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="M16" s="305" t="n">
-        <v>0.349</v>
-      </c>
-      <c r="N16" s="288" t="n">
-        <v>0.321</v>
-      </c>
-      <c r="O16" s="296" t="n">
-        <v>0.687487</v>
-      </c>
-      <c r="P16" s="278" t="n"/>
-    </row>
-    <row r="17" ht="19.5" customHeight="1" s="273">
-      <c r="A17" s="306" t="inlineStr">
+      <c r="K16" s="739" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="L16" s="739" t="n">
+        <v>0.4127673678748312</v>
+      </c>
+      <c r="M16" s="740" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="N16" s="740" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="O16" s="741" t="n">
+        <v>10129</v>
+      </c>
+      <c r="P16" s="719" t="n"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1" s="273">
+      <c r="A17" s="742" t="inlineStr">
         <is>
           <t>TOTAL / AVG</t>
         </is>
       </c>
-      <c r="B17" s="307">
-        <f>B16</f>
-        <v/>
-      </c>
-      <c r="C17" s="308">
+      <c r="B17" s="743" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" s="743">
         <f>SUM(C5:C16)</f>
         <v/>
       </c>
-      <c r="D17" s="308">
+      <c r="D17" s="743">
         <f>SUM(D5:D16)</f>
         <v/>
       </c>
-      <c r="E17" s="308">
+      <c r="E17" s="743">
         <f>SUM(E5:E16)</f>
         <v/>
       </c>
-      <c r="F17" s="309">
+      <c r="F17" s="743">
         <f>SUM(F5:F16)</f>
         <v/>
       </c>
-      <c r="G17" s="310">
-        <f>SUM(F5:F16)</f>
-        <v/>
-      </c>
-      <c r="H17" s="310">
+      <c r="G17" s="743">
         <f>AVERAGE(G5:G16)</f>
         <v/>
       </c>
-      <c r="I17" s="311">
+      <c r="H17" s="744">
         <f>AVERAGE(H5:H16)</f>
         <v/>
       </c>
-      <c r="J17" s="310">
+      <c r="I17" s="743">
         <f>SUM(I5:I16)</f>
         <v/>
       </c>
-      <c r="K17" s="312">
-        <f>AVERAGE(J5:J16)</f>
+      <c r="J17" s="745">
+        <f>C17/F17</f>
         <v/>
       </c>
-      <c r="L17" s="312">
-        <f>AVERAGE(K5:K16)</f>
+      <c r="K17" s="745">
+        <f>D17/F17</f>
         <v/>
       </c>
-      <c r="M17" s="312">
-        <f>AVERAGE(L5:L16)</f>
+      <c r="L17" s="745">
+        <f>E17/F17</f>
         <v/>
       </c>
-      <c r="N17" s="313">
+      <c r="M17" s="746">
         <f>AVERAGE(M5:M16)</f>
         <v/>
       </c>
-      <c r="O17" s="314" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P17" s="278" t="n"/>
+      <c r="N17" s="746">
+        <f>AVERAGE(N5:N16)</f>
+        <v/>
+      </c>
+      <c r="O17" s="747">
+        <f>AVERAGE(O5:O16)</f>
+        <v/>
+      </c>
+      <c r="P17" s="719" t="n"/>
     </row>
     <row r="18" ht="6" customHeight="1" s="273">
-      <c r="A18" s="315" t="inlineStr">
-        <is>
-          <t>† Mar 2026 = FORECAST based on 30-day actuals (10312.3 bbls/day avg) + steady run-rate through Mar 31. Actuals through Mar 30 from daily Cadiz Ops LOGS emails. Dec 2025 cost is negative due to 71k payroll reversal.
-*  Adj Pump Util % = pump runtime hours ÷ true available hours (21 hrs/day).
-**  % of Rail Cap/Day = avg bbls/day ÷ 15,000 bbl daily rail ceiling.</t>
-        </is>
-      </c>
+      <c r="A18" s="711" t="n"/>
+      <c r="B18" s="711" t="n"/>
+      <c r="C18" s="711" t="n"/>
+      <c r="D18" s="711" t="n"/>
+      <c r="E18" s="711" t="n"/>
+      <c r="F18" s="711" t="n"/>
+      <c r="G18" s="711" t="n"/>
+      <c r="H18" s="711" t="n"/>
+      <c r="I18" s="711" t="n"/>
+      <c r="J18" s="711" t="n"/>
+      <c r="K18" s="711" t="n"/>
+      <c r="L18" s="711" t="n"/>
+      <c r="M18" s="711" t="n"/>
+      <c r="N18" s="711" t="n"/>
+      <c r="O18" s="711" t="n"/>
+      <c r="P18" s="711" t="n"/>
     </row>
     <row r="19" ht="60" customHeight="1" s="273">
-      <c r="A19" s="316" t="inlineStr">
-        <is>
-          <t>† Mar 2026 = FORECAST based on 19-day actuals (10,522 bbls/day avg) + steady run-rate through Mar 31. Actuals through Mar 19 from daily Cadiz Ops LOGS emails. Dec 2025 cost is negative due to 71k payroll reversal.
-*  Adj Pump Util % = pump runtime hours ÷ true available hours (21 hrs/day).  True available = 24 hrs minus the 3-hr nightly railroad switch window during which pumps are idle.
-**  % of Rail Cap/Day = avg bbls/day ÷ 15,000 bbl daily rail ceiling.</t>
-        </is>
-      </c>
+      <c r="A19" s="748" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1" s="273"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A3:R3"/>
-    <mergeCell ref="A19:R19"/>
     <mergeCell ref="A1:R2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -3330,760 +4695,990 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:D70"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.71484375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="42" customWidth="1" style="272" min="1" max="1"/>
     <col width="20" customWidth="1" style="272" min="2" max="3"/>
+    <col width="13" customWidth="1" style="273" min="3" max="3"/>
+    <col width="13" customWidth="1" style="273" min="4" max="4"/>
+    <col width="13" customWidth="1" style="273" min="5" max="5"/>
+    <col width="13" customWidth="1" style="273" min="6" max="6"/>
+    <col width="13" customWidth="1" style="273" min="7" max="7"/>
+    <col width="13" customWidth="1" style="273" min="8" max="8"/>
+    <col width="13" customWidth="1" style="273" min="9" max="9"/>
+    <col width="13" customWidth="1" style="273" min="10" max="10"/>
+    <col width="13" customWidth="1" style="273" min="11" max="11"/>
+    <col width="13" customWidth="1" style="273" min="12" max="12"/>
+    <col width="13" customWidth="1" style="273" min="13" max="13"/>
+    <col width="13" customWidth="1" style="273" min="14" max="14"/>
+    <col width="13" customWidth="1" style="273" min="15" max="15"/>
+    <col width="13" customWidth="1" style="273" min="16" max="16"/>
+    <col width="13" customWidth="1" style="273" min="17" max="17"/>
+    <col width="13" customWidth="1" style="273" min="18" max="18"/>
+    <col width="13" customWidth="1" style="273" min="19" max="19"/>
+    <col width="13" customWidth="1" style="273" min="20" max="20"/>
+    <col width="13" customWidth="1" style="273" min="21" max="21"/>
+    <col width="13" customWidth="1" style="273" min="22" max="22"/>
+    <col width="13" customWidth="1" style="273" min="23" max="23"/>
+    <col width="13" customWidth="1" style="273" min="24" max="24"/>
+    <col width="13" customWidth="1" style="273" min="25" max="25"/>
+    <col width="13" customWidth="1" style="273" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="273">
-      <c r="A1" s="274" t="inlineStr">
-        <is>
-          <t>|  MARCH 2026 FORECASTED PROFIT &amp; LOSS  |  Accrual Basis</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="3.75" customHeight="1" s="273"/>
+      <c r="A1" s="749" t="inlineStr">
+        <is>
+          <t>|  APRIL 2026 FORECASTED PROFIT &amp; LOSS  |  Accrual Basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="3.75" customHeight="1" s="273">
+      <c r="A2" s="784" t="n"/>
+      <c r="B2" s="784" t="n"/>
+      <c r="C2" s="784" t="n"/>
+      <c r="D2" s="784" t="n"/>
+    </row>
     <row r="3" ht="21.75" customHeight="1" s="273">
-      <c r="A3" s="317" t="inlineStr">
+      <c r="A3" s="750" t="inlineStr">
         <is>
           <t>Account</t>
         </is>
       </c>
-      <c r="B3" s="317" t="inlineStr">
-        <is>
-          <t>Mar 2026 (Forecast)</t>
-        </is>
-      </c>
-      <c r="C3" s="317" t="inlineStr">
+      <c r="B3" s="750" t="inlineStr">
+        <is>
+          <t>Apr 2026 (Forecast)</t>
+        </is>
+      </c>
+      <c r="C3" s="750" t="inlineStr">
+        <is>
+          <t>Mar 2026 (Final Forecast)</t>
+        </is>
+      </c>
+      <c r="D3" s="750" t="inlineStr">
         <is>
           <t>Feb 2026 (Actual)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" s="273">
-      <c r="A4" s="306" t="inlineStr">
+      <c r="A4" s="751" t="inlineStr">
         <is>
           <t>INCOME</t>
         </is>
       </c>
-      <c r="B4" s="318" t="n"/>
-      <c r="C4" s="318" t="n"/>
+      <c r="B4" s="752" t="n"/>
+      <c r="C4" s="752" t="n"/>
+      <c r="D4" s="752" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1" s="273">
-      <c r="A5" s="319" t="inlineStr">
+      <c r="A5" s="753" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="B5" s="320" t="n">
+      <c r="B5" s="754" t="n">
+        <v>407307</v>
+      </c>
+      <c r="C5" s="754" t="n">
         <v>359659.19</v>
       </c>
-      <c r="C5" s="320" t="n">
+      <c r="D5" s="754" t="n">
         <v>344761.31</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" s="273">
-      <c r="A6" s="321" t="inlineStr">
+      <c r="A6" s="755" t="inlineStr">
         <is>
           <t>Uncategorized Income</t>
         </is>
       </c>
-      <c r="B6" s="322" t="n">
+      <c r="B6" s="756" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="322" t="n">
+      <c r="C6" s="756" t="n">
         <v>0</v>
       </c>
+      <c r="D6" s="756" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" ht="18" customHeight="1" s="273">
-      <c r="A7" s="323" t="inlineStr">
+      <c r="A7" s="757" t="inlineStr">
         <is>
           <t>Total Income</t>
         </is>
       </c>
-      <c r="B7" s="324" t="n">
-        <v>359659.19</v>
-      </c>
-      <c r="C7" s="324" t="n">
-        <v>344761.32</v>
+      <c r="B7" s="758">
+        <f>SUM(B5:B6)</f>
+        <v/>
+      </c>
+      <c r="C7" s="758">
+        <f>SUM(C5:C6)</f>
+        <v/>
+      </c>
+      <c r="D7" s="758">
+        <f>SUM(D5:D6)</f>
+        <v/>
       </c>
     </row>
     <row r="8" ht="6" customHeight="1" s="273"/>
     <row r="9" ht="18" customHeight="1" s="273">
-      <c r="A9" s="306" t="inlineStr">
+      <c r="A9" s="751" t="inlineStr">
         <is>
           <t>COST OF GOODS SOLD</t>
         </is>
       </c>
-      <c r="B9" s="318" t="n"/>
-      <c r="C9" s="318" t="n"/>
+      <c r="B9" s="752" t="n"/>
+      <c r="C9" s="752" t="n"/>
+      <c r="D9" s="752" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1" s="273">
-      <c r="A10" s="321" t="inlineStr">
+      <c r="A10" s="755" t="inlineStr">
         <is>
           <t xml:space="preserve">  Diesel</t>
         </is>
       </c>
-      <c r="B10" s="322" t="n">
+      <c r="B10" s="756" t="n">
+        <v>3971.37</v>
+      </c>
+      <c r="C10" s="756" t="n">
         <v>3172.49</v>
       </c>
-      <c r="C10" s="322" t="n">
+      <c r="D10" s="756" t="n">
         <v>4220.02</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" s="273">
-      <c r="A11" s="319" t="inlineStr">
+      <c r="A11" s="753" t="inlineStr">
         <is>
           <t xml:space="preserve">  Equipment Rental - COGS</t>
         </is>
       </c>
-      <c r="B11" s="320" t="n">
+      <c r="B11" s="754" t="n">
+        <v>31272.86</v>
+      </c>
+      <c r="C11" s="754" t="n">
         <v>28946.24</v>
       </c>
-      <c r="C11" s="320" t="n">
+      <c r="D11" s="754" t="n">
         <v>27326.76</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" s="273">
-      <c r="A12" s="321" t="inlineStr">
+      <c r="A12" s="755" t="inlineStr">
         <is>
           <t xml:space="preserve">  Hourly Wages</t>
         </is>
       </c>
-      <c r="B12" s="322" t="n">
+      <c r="B12" s="756" t="n">
+        <v>60806.81</v>
+      </c>
+      <c r="C12" s="756" t="n">
         <v>66654.99000000001</v>
       </c>
-      <c r="C12" s="322" t="n">
+      <c r="D12" s="756" t="n">
         <v>60806.81</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" s="273">
-      <c r="A13" s="319" t="inlineStr">
+      <c r="A13" s="753" t="inlineStr">
         <is>
           <t xml:space="preserve">  Payroll Taxes - COGS</t>
         </is>
       </c>
-      <c r="B13" s="320" t="n">
+      <c r="B13" s="754" t="n">
+        <v>5509.84</v>
+      </c>
+      <c r="C13" s="754" t="n">
         <v>6038.94</v>
       </c>
-      <c r="C13" s="320" t="n">
+      <c r="D13" s="754" t="n">
         <v>5509.84</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1" s="273">
-      <c r="A14" s="323" t="inlineStr">
+      <c r="A14" s="757" t="inlineStr">
         <is>
           <t>Total COGS</t>
         </is>
       </c>
-      <c r="B14" s="324">
+      <c r="B14" s="758">
         <f>SUM(B10:B13)</f>
         <v/>
       </c>
-      <c r="C14" s="324" t="n">
-        <v>97863.42999999999</v>
+      <c r="C14" s="758">
+        <f>SUM(C10:C13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="758">
+        <f>SUM(D10:D13)</f>
+        <v/>
       </c>
     </row>
     <row r="15" ht="6" customHeight="1" s="273"/>
     <row r="16" ht="18" customHeight="1" s="273">
-      <c r="A16" s="323" t="inlineStr">
+      <c r="A16" s="757" t="inlineStr">
         <is>
           <t>GROSS PROFIT</t>
         </is>
       </c>
-      <c r="B16" s="324">
+      <c r="B16" s="758">
         <f>B7-B14</f>
         <v/>
       </c>
-      <c r="C16" s="324" t="n">
-        <v>246897.89</v>
+      <c r="C16" s="758">
+        <f>C7-C14</f>
+        <v/>
+      </c>
+      <c r="D16" s="758">
+        <f>D7-D14</f>
+        <v/>
       </c>
     </row>
     <row r="17" ht="6" customHeight="1" s="273"/>
     <row r="18" ht="18" customHeight="1" s="273">
-      <c r="A18" s="306" t="inlineStr">
+      <c r="A18" s="751" t="inlineStr">
         <is>
           <t>EXPENSES</t>
         </is>
       </c>
-      <c r="B18" s="318" t="n"/>
-      <c r="C18" s="318" t="n"/>
+      <c r="B18" s="752" t="n"/>
+      <c r="C18" s="752" t="n"/>
+      <c r="D18" s="752" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1" s="273">
-      <c r="A19" s="319" t="inlineStr">
+      <c r="A19" s="753" t="inlineStr">
         <is>
           <t xml:space="preserve">  Advertising &amp; Marketing</t>
         </is>
       </c>
-      <c r="B19" s="320" t="n">
+      <c r="B19" s="754" t="n">
+        <v>1926.09</v>
+      </c>
+      <c r="C19" s="754" t="n">
         <v>248.32</v>
       </c>
-      <c r="C19" s="320" t="n">
+      <c r="D19" s="754" t="n">
         <v>248.32</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" s="273">
-      <c r="A20" s="321" t="inlineStr">
+      <c r="A20" s="755" t="inlineStr">
         <is>
           <t xml:space="preserve">  Commissions &amp; Fees</t>
         </is>
       </c>
-      <c r="B20" s="322" t="n">
+      <c r="B20" s="756" t="n">
+        <v>229.48</v>
+      </c>
+      <c r="C20" s="756" t="n">
         <v>215.91</v>
       </c>
-      <c r="C20" s="322" t="n">
+      <c r="D20" s="756" t="n">
         <v>215.91</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1" s="273">
-      <c r="A21" s="319" t="inlineStr">
+      <c r="A21" s="753" t="inlineStr">
         <is>
           <t xml:space="preserve">  Contract Labor</t>
         </is>
       </c>
-      <c r="B21" s="320" t="n">
+      <c r="B21" s="754" t="n">
+        <v>9009.1</v>
+      </c>
+      <c r="C21" s="754" t="n">
         <v>9018.200000000001</v>
       </c>
-      <c r="C21" s="320" t="n">
+      <c r="D21" s="754" t="n">
         <v>9018.200000000001</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1" s="273">
-      <c r="A22" s="321" t="inlineStr">
+      <c r="A22" s="755" t="inlineStr">
         <is>
           <t xml:space="preserve">  Equipment Calibration</t>
         </is>
       </c>
-      <c r="B22" s="322" t="n">
+      <c r="B22" s="756" t="n">
         <v>4062.2</v>
       </c>
-      <c r="C22" s="322" t="n">
+      <c r="C22" s="756" t="n">
         <v>4062.2</v>
       </c>
+      <c r="D22" s="756" t="n">
+        <v>4062.2</v>
+      </c>
     </row>
     <row r="23" ht="18" customHeight="1" s="273">
-      <c r="A23" s="325" t="inlineStr">
+      <c r="A23" s="759" t="inlineStr">
         <is>
           <t xml:space="preserve">  General Business Expenses</t>
         </is>
       </c>
-      <c r="B23" s="326" t="n"/>
-      <c r="C23" s="326" t="n"/>
+      <c r="B23" s="760" t="n"/>
+      <c r="C23" s="760" t="n"/>
+      <c r="D23" s="760" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1" s="273">
-      <c r="A24" s="327" t="inlineStr">
+      <c r="A24" s="761" t="inlineStr">
         <is>
           <t xml:space="preserve">    Memberships &amp; Subscriptions</t>
         </is>
       </c>
-      <c r="B24" s="322" t="n">
+      <c r="B24" s="756" t="n">
+        <v>385.84</v>
+      </c>
+      <c r="C24" s="756" t="n">
         <v>189.74</v>
       </c>
-      <c r="C24" s="322" t="n">
+      <c r="D24" s="756" t="n">
         <v>189.74</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1" s="273">
-      <c r="A25" s="328" t="inlineStr">
+      <c r="A25" s="762" t="inlineStr">
         <is>
           <t xml:space="preserve">    Site Services</t>
         </is>
       </c>
-      <c r="B25" s="320" t="n">
+      <c r="B25" s="754" t="n">
+        <v>1096.45</v>
+      </c>
+      <c r="C25" s="754" t="n">
         <v>2130</v>
       </c>
-      <c r="C25" s="320" t="n">
+      <c r="D25" s="754" t="n">
         <v>2130</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1" s="273">
-      <c r="A26" s="329" t="inlineStr">
+      <c r="A26" s="763" t="inlineStr">
         <is>
           <t xml:space="preserve">  Total General Business</t>
         </is>
       </c>
-      <c r="B26" s="324">
+      <c r="B26" s="758">
         <f>B24+B25</f>
         <v/>
       </c>
-      <c r="C26" s="324">
+      <c r="C26" s="758">
         <f>C24+C25</f>
         <v/>
       </c>
+      <c r="D26" s="758">
+        <f>D24+D25</f>
+        <v/>
+      </c>
     </row>
     <row r="27" ht="18" customHeight="1" s="273">
-      <c r="A27" s="319" t="inlineStr">
+      <c r="A27" s="753" t="inlineStr">
         <is>
           <t xml:space="preserve">  Meals</t>
         </is>
       </c>
-      <c r="B27" s="320" t="n">
+      <c r="B27" s="754" t="n">
+        <v>170.36</v>
+      </c>
+      <c r="C27" s="754" t="n">
         <v>228.6</v>
       </c>
-      <c r="C27" s="320" t="n">
+      <c r="D27" s="754" t="n">
         <v>228.6</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="273">
-      <c r="A28" s="330" t="inlineStr">
+      <c r="A28" s="764" t="inlineStr">
         <is>
           <t xml:space="preserve">  Office Expenses</t>
         </is>
       </c>
-      <c r="B28" s="331" t="n"/>
-      <c r="C28" s="331" t="n"/>
+      <c r="B28" s="765" t="n"/>
+      <c r="C28" s="765" t="n"/>
+      <c r="D28" s="765" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1" s="273">
-      <c r="A29" s="328" t="inlineStr">
+      <c r="A29" s="762" t="inlineStr">
         <is>
           <t xml:space="preserve">    Small Tools &amp; Equipment</t>
         </is>
       </c>
-      <c r="B29" s="320" t="n">
+      <c r="B29" s="754" t="n">
+        <v>78.81999999999999</v>
+      </c>
+      <c r="C29" s="754" t="n">
         <v>137.51</v>
       </c>
-      <c r="C29" s="320" t="n">
+      <c r="D29" s="754" t="n">
         <v>137.51</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1" s="273">
-      <c r="A30" s="327" t="inlineStr">
+      <c r="A30" s="761" t="inlineStr">
         <is>
           <t xml:space="preserve">    Software &amp; Apps</t>
         </is>
       </c>
-      <c r="B30" s="322" t="n">
+      <c r="B30" s="756" t="n">
+        <v>154.69</v>
+      </c>
+      <c r="C30" s="756" t="n">
         <v>220.12</v>
       </c>
-      <c r="C30" s="322" t="n">
+      <c r="D30" s="756" t="n">
         <v>220.12</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1" s="273">
-      <c r="A31" s="329" t="inlineStr">
+      <c r="A31" s="763" t="inlineStr">
         <is>
           <t xml:space="preserve">  Total Office Expenses</t>
         </is>
       </c>
-      <c r="B31" s="324">
+      <c r="B31" s="758">
         <f>B29+B30</f>
         <v/>
       </c>
-      <c r="C31" s="324">
+      <c r="C31" s="758">
         <f>C29+C30</f>
         <v/>
       </c>
+      <c r="D31" s="758">
+        <f>D29+D30</f>
+        <v/>
+      </c>
     </row>
     <row r="32" ht="18" customHeight="1" s="273">
-      <c r="A32" s="330" t="inlineStr">
+      <c r="A32" s="764" t="inlineStr">
         <is>
           <t xml:space="preserve">  Payroll Expenses</t>
         </is>
       </c>
-      <c r="B32" s="331" t="n"/>
-      <c r="C32" s="331" t="n"/>
+      <c r="B32" s="765" t="n"/>
+      <c r="C32" s="765" t="n"/>
+      <c r="D32" s="765" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1" s="273">
-      <c r="A33" s="328" t="inlineStr">
+      <c r="A33" s="762" t="inlineStr">
         <is>
           <t xml:space="preserve">    Salaries</t>
         </is>
       </c>
-      <c r="B33" s="320" t="n">
+      <c r="B33" s="754" t="n">
+        <v>30496.99</v>
+      </c>
+      <c r="C33" s="754" t="n">
         <v>27955</v>
       </c>
-      <c r="C33" s="320" t="n">
+      <c r="D33" s="754" t="n">
         <v>27955</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1" s="273">
-      <c r="A34" s="327" t="inlineStr">
+      <c r="A34" s="761" t="inlineStr">
         <is>
           <t xml:space="preserve">    Taxes</t>
         </is>
       </c>
-      <c r="B34" s="322" t="n">
+      <c r="B34" s="756" t="n">
+        <v>6193.44</v>
+      </c>
+      <c r="C34" s="756" t="n">
         <v>6785.38</v>
       </c>
-      <c r="C34" s="322" t="n">
+      <c r="D34" s="756" t="n">
         <v>6193.44</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1" s="273">
-      <c r="A35" s="328" t="inlineStr">
+      <c r="A35" s="762" t="inlineStr">
         <is>
           <t xml:space="preserve">    Wages</t>
         </is>
       </c>
-      <c r="B35" s="320" t="n">
+      <c r="B35" s="754" t="n">
+        <v>26453.17</v>
+      </c>
+      <c r="C35" s="754" t="n">
         <v>28997.34</v>
       </c>
-      <c r="C35" s="320" t="n">
+      <c r="D35" s="754" t="n">
         <v>26453.17</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1" s="273">
-      <c r="A36" s="329" t="inlineStr">
+      <c r="A36" s="763" t="inlineStr">
         <is>
           <t xml:space="preserve">  Total Payroll Expenses</t>
         </is>
       </c>
-      <c r="B36" s="324">
-        <f>B33+B34+B35</f>
+      <c r="B36" s="758">
+        <f>SUM(B33:B35)</f>
         <v/>
       </c>
-      <c r="C36" s="324">
-        <f>C33+C34+C35</f>
+      <c r="C36" s="758">
+        <f>SUM(C33:C35)</f>
         <v/>
       </c>
+      <c r="D36" s="758">
+        <f>SUM(D33:D35)</f>
+        <v/>
+      </c>
     </row>
     <row r="37" ht="18" customHeight="1" s="273">
-      <c r="A37" s="325" t="inlineStr">
+      <c r="A37" s="759" t="inlineStr">
         <is>
           <t xml:space="preserve">  Rent</t>
         </is>
       </c>
-      <c r="B37" s="326" t="n"/>
-      <c r="C37" s="326" t="n"/>
+      <c r="B37" s="760" t="n"/>
+      <c r="C37" s="760" t="n"/>
+      <c r="D37" s="760" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1" s="273">
-      <c r="A38" s="327" t="inlineStr">
+      <c r="A38" s="761" t="inlineStr">
         <is>
           <t xml:space="preserve">    Building &amp; Land Rent</t>
         </is>
       </c>
-      <c r="B38" s="322" t="n">
+      <c r="B38" s="756" t="n">
         <v>9056.41</v>
       </c>
-      <c r="C38" s="322" t="n">
+      <c r="C38" s="756" t="n">
         <v>9056.41</v>
       </c>
+      <c r="D38" s="756" t="n">
+        <v>9056.41</v>
+      </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="273">
-      <c r="A39" s="332" t="inlineStr">
+      <c r="A39" s="766" t="inlineStr">
         <is>
           <t xml:space="preserve">    Rental Equipment</t>
         </is>
       </c>
-      <c r="B39" s="333" t="n">
+      <c r="B39" s="767" t="n">
+        <v>1311.67</v>
+      </c>
+      <c r="C39" s="767" t="n">
         <v>1619.48</v>
       </c>
-      <c r="C39" s="333" t="n">
+      <c r="D39" s="767" t="n">
         <v>1619.48</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1" s="273">
-      <c r="A40" s="329" t="inlineStr">
+      <c r="A40" s="763" t="inlineStr">
         <is>
           <t xml:space="preserve">  Total Rent</t>
         </is>
       </c>
-      <c r="B40" s="324">
+      <c r="B40" s="758">
         <f>B38+B39</f>
         <v/>
       </c>
-      <c r="C40" s="324" t="n">
-        <v>10675.89</v>
+      <c r="C40" s="758">
+        <f>C38+C39</f>
+        <v/>
+      </c>
+      <c r="D40" s="758">
+        <f>D38+D39</f>
+        <v/>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1" s="273">
-      <c r="A41" s="321" t="inlineStr">
+      <c r="A41" s="755" t="inlineStr">
         <is>
           <t xml:space="preserve">  Repairs &amp; Maintenance</t>
         </is>
       </c>
-      <c r="B41" s="322" t="n">
+      <c r="B41" s="756" t="n">
+        <v>37125.2</v>
+      </c>
+      <c r="C41" s="756" t="n">
         <v>32278.45</v>
       </c>
-      <c r="C41" s="322" t="n">
+      <c r="D41" s="756" t="n">
         <v>32278.45</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1" s="273">
-      <c r="A42" s="325" t="inlineStr">
+      <c r="A42" s="759" t="inlineStr">
         <is>
           <t xml:space="preserve">  Supplies</t>
         </is>
       </c>
-      <c r="B42" s="326" t="n"/>
-      <c r="C42" s="326" t="n"/>
+      <c r="B42" s="760" t="n"/>
+      <c r="C42" s="760" t="n"/>
+      <c r="D42" s="760" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1" s="273">
-      <c r="A43" s="327" t="inlineStr">
+      <c r="A43" s="761" t="inlineStr">
         <is>
           <t xml:space="preserve">    Office Supplies</t>
         </is>
       </c>
-      <c r="B43" s="322" t="n">
+      <c r="B43" s="756" t="n">
+        <v>3212.45</v>
+      </c>
+      <c r="C43" s="756" t="n">
         <v>2385.62</v>
       </c>
-      <c r="C43" s="322" t="n">
+      <c r="D43" s="756" t="n">
         <v>2385.62</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1" s="273">
-      <c r="A44" s="328" t="inlineStr">
+      <c r="A44" s="762" t="inlineStr">
         <is>
           <t xml:space="preserve">    Yard Expense</t>
         </is>
       </c>
-      <c r="B44" s="320" t="n">
+      <c r="B44" s="754" t="n">
+        <v>12582.99</v>
+      </c>
+      <c r="C44" s="754" t="n">
         <v>12018.9</v>
       </c>
-      <c r="C44" s="320" t="n">
+      <c r="D44" s="754" t="n">
         <v>12018.9</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1" s="273">
-      <c r="A45" s="329" t="inlineStr">
+      <c r="A45" s="763" t="inlineStr">
         <is>
           <t xml:space="preserve">  Total Supplies</t>
         </is>
       </c>
-      <c r="B45" s="324">
+      <c r="B45" s="758">
         <f>B43+B44</f>
         <v/>
       </c>
-      <c r="C45" s="324">
+      <c r="C45" s="758">
         <f>C43+C44</f>
         <v/>
       </c>
+      <c r="D45" s="758">
+        <f>D43+D44</f>
+        <v/>
+      </c>
     </row>
     <row r="46" ht="18" customHeight="1" s="273">
-      <c r="A46" s="325" t="inlineStr">
+      <c r="A46" s="759" t="inlineStr">
         <is>
           <t xml:space="preserve">  Utilities</t>
         </is>
       </c>
-      <c r="B46" s="326" t="n"/>
-      <c r="C46" s="326" t="n"/>
+      <c r="B46" s="760" t="n"/>
+      <c r="C46" s="760" t="n"/>
+      <c r="D46" s="760" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1" s="273">
-      <c r="A47" s="327" t="inlineStr">
+      <c r="A47" s="761" t="inlineStr">
         <is>
           <t xml:space="preserve">    Disposal &amp; Waste Fees</t>
         </is>
       </c>
-      <c r="B47" s="322" t="n">
+      <c r="B47" s="756" t="n">
         <v>271.09</v>
       </c>
-      <c r="C47" s="322" t="n">
+      <c r="C47" s="756" t="n">
         <v>271.09</v>
       </c>
+      <c r="D47" s="756" t="n">
+        <v>271.09</v>
+      </c>
     </row>
     <row r="48" ht="18" customHeight="1" s="273">
-      <c r="A48" s="328" t="inlineStr">
+      <c r="A48" s="762" t="inlineStr">
         <is>
           <t xml:space="preserve">    Electricity</t>
         </is>
       </c>
-      <c r="B48" s="320" t="n">
+      <c r="B48" s="754" t="n">
+        <v>1488.85</v>
+      </c>
+      <c r="C48" s="754" t="n">
         <v>1567.95</v>
       </c>
-      <c r="C48" s="320" t="n">
+      <c r="D48" s="754" t="n">
         <v>1567.95</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1" s="273">
-      <c r="A49" s="327" t="inlineStr">
+      <c r="A49" s="761" t="inlineStr">
         <is>
           <t xml:space="preserve">    Phone Service</t>
         </is>
       </c>
-      <c r="B49" s="322" t="n">
+      <c r="B49" s="756" t="n">
+        <v>432.21</v>
+      </c>
+      <c r="C49" s="756" t="n">
         <v>384.64</v>
       </c>
-      <c r="C49" s="322" t="n">
+      <c r="D49" s="756" t="n">
         <v>384.64</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1" s="273">
-      <c r="A50" s="329" t="inlineStr">
+      <c r="A50" s="763" t="inlineStr">
         <is>
           <t xml:space="preserve">  Total Utilities</t>
         </is>
       </c>
-      <c r="B50" s="324">
-        <f>B47+B48+B49</f>
+      <c r="B50" s="758">
+        <f>SUM(B47:B49)</f>
         <v/>
       </c>
-      <c r="C50" s="324">
-        <f>C47+C48+C49</f>
+      <c r="C50" s="758">
+        <f>SUM(C47:C49)</f>
         <v/>
       </c>
+      <c r="D50" s="758">
+        <f>SUM(D47:D49)</f>
+        <v/>
+      </c>
     </row>
     <row r="51" ht="6" customHeight="1" s="273">
-      <c r="A51" s="323" t="inlineStr">
+      <c r="A51" s="757" t="inlineStr">
         <is>
           <t>Total Expenses</t>
         </is>
       </c>
-      <c r="B51" s="324">
+      <c r="B51" s="758">
         <f>B19+B20+B21+B22+B26+B27+B31+B36+B40+B41+B45+B50</f>
         <v/>
       </c>
-      <c r="C51" s="324">
+      <c r="C51" s="758">
         <f>C19+C20+C21+C22+C26+C27+C31+C36+C40+C41+C45+C50</f>
         <v/>
       </c>
+      <c r="D51" s="758">
+        <f>D19+D20+D21+D22+D26+D27+D31+D36+D40+D41+D45+D50</f>
+        <v/>
+      </c>
     </row>
     <row r="52" ht="18" customHeight="1" s="273"/>
     <row r="53" ht="6" customHeight="1" s="273">
-      <c r="A53" s="323" t="inlineStr">
+      <c r="A53" s="757" t="inlineStr">
         <is>
           <t>NET OPERATING INCOME</t>
         </is>
       </c>
-      <c r="B53" s="324">
+      <c r="B53" s="758">
         <f>B16-B51</f>
         <v/>
       </c>
-      <c r="C53" s="324">
+      <c r="C53" s="758">
         <f>C16-C51</f>
         <v/>
       </c>
+      <c r="D53" s="758">
+        <f>D16-D51</f>
+        <v/>
+      </c>
     </row>
     <row r="54" ht="18" customHeight="1" s="273"/>
     <row r="55" ht="18" customHeight="1" s="273">
-      <c r="A55" s="306" t="inlineStr">
+      <c r="A55" s="751" t="inlineStr">
         <is>
           <t>OTHER EXPENSES</t>
         </is>
       </c>
-      <c r="B55" s="318" t="n"/>
-      <c r="C55" s="318" t="n"/>
+      <c r="B55" s="752" t="n"/>
+      <c r="C55" s="752" t="n"/>
+      <c r="D55" s="752" t="n"/>
     </row>
     <row r="56" ht="18" customHeight="1" s="273">
-      <c r="A56" s="319" t="inlineStr">
+      <c r="A56" s="753" t="inlineStr">
         <is>
           <t xml:space="preserve">  Misc / Ask</t>
         </is>
       </c>
-      <c r="B56" s="320" t="n">
+      <c r="B56" s="754" t="n">
         <v>215.86</v>
       </c>
-      <c r="C56" s="320" t="n">
+      <c r="C56" s="754" t="n">
         <v>215.86</v>
       </c>
+      <c r="D56" s="754" t="n">
+        <v>215.86</v>
+      </c>
     </row>
     <row r="57" ht="18" customHeight="1" s="273">
-      <c r="A57" s="330" t="inlineStr">
+      <c r="A57" s="764" t="inlineStr">
         <is>
           <t xml:space="preserve">  Vehicle Expenses</t>
         </is>
       </c>
-      <c r="B57" s="334" t="n">
+      <c r="B57" s="768" t="n">
+        <v>392.17</v>
+      </c>
+      <c r="C57" s="768" t="n">
         <v>47.67</v>
       </c>
-      <c r="C57" s="334" t="n">
+      <c r="D57" s="768" t="n">
         <v>47.67</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1" s="273">
-      <c r="A58" s="328" t="inlineStr">
+      <c r="A58" s="762" t="inlineStr">
         <is>
           <t xml:space="preserve">    Parking &amp; Tolls</t>
         </is>
       </c>
-      <c r="B58" s="320" t="n">
+      <c r="B58" s="754" t="n">
+        <v>340.27</v>
+      </c>
+      <c r="C58" s="754" t="n">
         <v>140</v>
       </c>
-      <c r="C58" s="320" t="n">
+      <c r="D58" s="754" t="n">
         <v>140</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1" s="273">
-      <c r="A59" s="327" t="inlineStr">
+      <c r="A59" s="761" t="inlineStr">
         <is>
           <t xml:space="preserve">    Vehicle Gas &amp; Fuel</t>
         </is>
       </c>
-      <c r="B59" s="322" t="n">
+      <c r="B59" s="756" t="n">
+        <v>1190.86</v>
+      </c>
+      <c r="C59" s="756" t="n">
         <v>971.0700000000001</v>
       </c>
-      <c r="C59" s="322" t="n">
+      <c r="D59" s="756" t="n">
         <v>971.0700000000001</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1" s="273">
-      <c r="A60" s="328" t="inlineStr">
+      <c r="A60" s="762" t="inlineStr">
         <is>
           <t xml:space="preserve">    Vehicle Repairs</t>
         </is>
       </c>
-      <c r="B60" s="320" t="n">
+      <c r="B60" s="754" t="n">
         <v>5938.73</v>
       </c>
-      <c r="C60" s="320" t="n">
+      <c r="C60" s="754" t="n">
         <v>5938.73</v>
       </c>
+      <c r="D60" s="754" t="n">
+        <v>5938.73</v>
+      </c>
     </row>
     <row r="61" ht="18" customHeight="1" s="273">
-      <c r="A61" s="329" t="inlineStr">
+      <c r="A61" s="763" t="inlineStr">
         <is>
           <t xml:space="preserve">  Total Vehicle Expenses</t>
         </is>
       </c>
-      <c r="B61" s="324">
-        <f>B57+B58+B59+B60</f>
+      <c r="B61" s="758">
+        <f>SUM(B57:B60)</f>
         <v/>
       </c>
-      <c r="C61" s="324">
-        <f>C57+C58+C59+C60</f>
+      <c r="C61" s="758">
+        <f>SUM(C57:C60)</f>
         <v/>
       </c>
+      <c r="D61" s="758">
+        <f>SUM(D57:D60)</f>
+        <v/>
+      </c>
     </row>
     <row r="62" ht="18" customHeight="1" s="273">
-      <c r="A62" s="323" t="inlineStr">
+      <c r="A62" s="757" t="inlineStr">
         <is>
           <t>Total Other Expenses</t>
         </is>
       </c>
-      <c r="B62" s="324">
+      <c r="B62" s="758">
         <f>B56+B61</f>
         <v/>
       </c>
-      <c r="C62" s="324">
+      <c r="C62" s="758">
         <f>C56+C61</f>
         <v/>
       </c>
+      <c r="D62" s="758">
+        <f>D56+D61</f>
+        <v/>
+      </c>
     </row>
     <row r="63" ht="6" customHeight="1" s="273">
-      <c r="A63" s="323" t="inlineStr">
+      <c r="A63" s="757" t="inlineStr">
         <is>
           <t>Net Other Income</t>
         </is>
       </c>
-      <c r="B63" s="324">
+      <c r="B63" s="758">
         <f>-B62</f>
         <v/>
       </c>
-      <c r="C63" s="324">
+      <c r="C63" s="758">
         <f>-C62</f>
         <v/>
       </c>
+      <c r="D63" s="758">
+        <f>-D62</f>
+        <v/>
+      </c>
     </row>
     <row r="64" ht="18" customHeight="1" s="273"/>
     <row r="65" ht="15" customHeight="1" s="273">
-      <c r="A65" s="335" t="inlineStr">
+      <c r="A65" s="769" t="inlineStr">
         <is>
           <t>NET INCOME</t>
         </is>
       </c>
-      <c r="B65" s="336">
+      <c r="B65" s="770">
         <f>B53+B63</f>
         <v/>
       </c>
-      <c r="C65" s="336">
+      <c r="C65" s="770">
         <f>C53+C63</f>
         <v/>
       </c>
+      <c r="D65" s="770">
+        <f>D53+D63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="771" t="inlineStr">
+        <is>
+          <t>NOTES:</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="772" t="inlineStr">
+        <is>
+          <t>Feb 2026 = Actual P&amp;L from QuickBooks (accrual basis).</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="772" t="inlineStr">
+        <is>
+          <t>Mar 2026 = Final forecast based on 31-day run rate (10,312 bbls/day avg through Mar 30, extrapolated through Mar 31).</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="772" t="inlineStr">
+        <is>
+          <t>Apr 2026 = Expenses from Jan/Feb P&amp;L avg. Revenue = 368,079 bbls × $1.107/bbl (Feb-Mar trailing avg). COGS payroll uses Feb structure.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="A1:D2"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4097,7 +5692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.71484375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="272" min="1" max="1"/>
@@ -4105,270 +5700,417 @@
     <col width="8" customWidth="1" style="272" min="3" max="3"/>
     <col width="28" customWidth="1" style="272" min="4" max="4"/>
     <col width="18" customWidth="1" style="272" min="5" max="7"/>
+    <col width="13" customWidth="1" style="273" min="6" max="6"/>
+    <col width="13" customWidth="1" style="273" min="7" max="7"/>
     <col width="14" customWidth="1" style="272" min="8" max="8"/>
+    <col width="13" customWidth="1" style="273" min="9" max="9"/>
+    <col width="13" customWidth="1" style="273" min="10" max="10"/>
+    <col width="13" customWidth="1" style="273" min="11" max="11"/>
+    <col width="13" customWidth="1" style="273" min="12" max="12"/>
+    <col width="13" customWidth="1" style="273" min="13" max="13"/>
+    <col width="13" customWidth="1" style="273" min="14" max="14"/>
+    <col width="13" customWidth="1" style="273" min="15" max="15"/>
+    <col width="13" customWidth="1" style="273" min="16" max="16"/>
+    <col width="13" customWidth="1" style="273" min="17" max="17"/>
+    <col width="13" customWidth="1" style="273" min="18" max="18"/>
+    <col width="13" customWidth="1" style="273" min="19" max="19"/>
+    <col width="13" customWidth="1" style="273" min="20" max="20"/>
+    <col width="13" customWidth="1" style="273" min="21" max="21"/>
+    <col width="13" customWidth="1" style="273" min="22" max="22"/>
+    <col width="13" customWidth="1" style="273" min="23" max="23"/>
+    <col width="13" customWidth="1" style="273" min="24" max="24"/>
+    <col width="13" customWidth="1" style="273" min="25" max="25"/>
+    <col width="13" customWidth="1" style="273" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="273">
-      <c r="A1" s="274" t="inlineStr">
-        <is>
-          <t>|  MARCH 2026 WEEKLY BREAKDOWN</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15" customHeight="1" s="273"/>
+      <c r="A1" s="708" t="inlineStr">
+        <is>
+          <t>|  APRIL 2026 WEEKLY BREAKDOWN</t>
+        </is>
+      </c>
+      <c r="I1" s="552" t="n"/>
+      <c r="J1" s="552" t="n"/>
+    </row>
+    <row r="2" ht="15" customHeight="1" s="273">
+      <c r="I2" s="552" t="n"/>
+      <c r="J2" s="552" t="n"/>
+    </row>
     <row r="3" ht="21.75" customHeight="1" s="273">
-      <c r="A3" s="317" t="inlineStr">
+      <c r="A3" s="750" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="B3" s="317" t="inlineStr">
+      <c r="B3" s="750" t="inlineStr">
         <is>
           <t>Dates</t>
         </is>
       </c>
-      <c r="C3" s="317" t="inlineStr">
+      <c r="C3" s="750" t="inlineStr">
         <is>
           <t>Days</t>
         </is>
       </c>
-      <c r="D3" s="317" t="inlineStr">
+      <c r="D3" s="750" t="inlineStr">
         <is>
           <t>Bbls (Actual / Forecast)</t>
         </is>
       </c>
-      <c r="E3" s="317" t="inlineStr">
+      <c r="E3" s="750" t="inlineStr">
         <is>
           <t>Revenue ($)</t>
         </is>
       </c>
-      <c r="F3" s="317" t="inlineStr">
+      <c r="F3" s="750" t="inlineStr">
         <is>
           <t>Expenses ($)</t>
         </is>
       </c>
-      <c r="G3" s="317" t="inlineStr">
+      <c r="G3" s="750" t="inlineStr">
         <is>
           <t>Net ($)</t>
         </is>
       </c>
-      <c r="H3" s="317" t="inlineStr">
+      <c r="H3" s="750" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
+      <c r="I3" s="552" t="n"/>
+      <c r="J3" s="552" t="n"/>
     </row>
     <row r="4" ht="19.5" customHeight="1" s="273">
-      <c r="A4" s="290" t="inlineStr">
+      <c r="A4" s="773" t="inlineStr">
         <is>
           <t>Week 1</t>
         </is>
       </c>
-      <c r="B4" s="290" t="inlineStr">
-        <is>
-          <t>Mar 1–7</t>
-        </is>
-      </c>
-      <c r="C4" s="290" t="n">
+      <c r="B4" s="773" t="inlineStr">
+        <is>
+          <t>Apr 1–7</t>
+        </is>
+      </c>
+      <c r="C4" s="773" t="n">
         <v>7</v>
       </c>
-      <c r="D4" s="337" t="inlineStr">
-        <is>
-          <t>Actual: 89,929</t>
-        </is>
-      </c>
-      <c r="E4" s="291" t="n">
-        <v>97412</v>
-      </c>
-      <c r="F4" s="291" t="n">
-        <v>30487</v>
-      </c>
-      <c r="G4" s="291">
+      <c r="D4" s="774" t="inlineStr">
+        <is>
+          <t>85,883</t>
+        </is>
+      </c>
+      <c r="E4" s="775" t="n">
+        <v>95072</v>
+      </c>
+      <c r="F4" s="775" t="n">
+        <v>64358</v>
+      </c>
+      <c r="G4" s="775">
         <f>E4-F4</f>
         <v/>
       </c>
-      <c r="H4" s="338" t="inlineStr">
-        <is>
-          <t>ACTUAL</t>
-        </is>
-      </c>
+      <c r="H4" s="776" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="I4" s="552" t="n"/>
+      <c r="J4" s="552" t="n"/>
     </row>
     <row r="5" ht="19.5" customHeight="1" s="273">
-      <c r="A5" s="280" t="inlineStr">
+      <c r="A5" s="777" t="inlineStr">
         <is>
           <t>Week 2</t>
         </is>
       </c>
-      <c r="B5" s="280" t="inlineStr">
-        <is>
-          <t>Mar 8–14</t>
-        </is>
-      </c>
-      <c r="C5" s="280" t="n">
+      <c r="B5" s="777" t="inlineStr">
+        <is>
+          <t>Apr 8–14</t>
+        </is>
+      </c>
+      <c r="C5" s="777" t="n">
         <v>7</v>
       </c>
-      <c r="D5" s="339" t="inlineStr">
-        <is>
-          <t>Actual: 79,514</t>
-        </is>
-      </c>
-      <c r="E5" s="281" t="n">
-        <v>85885</v>
-      </c>
-      <c r="F5" s="281" t="n">
-        <v>30487</v>
-      </c>
-      <c r="G5" s="281">
+      <c r="D5" s="778" t="inlineStr">
+        <is>
+          <t>85,883</t>
+        </is>
+      </c>
+      <c r="E5" s="779" t="n">
+        <v>95072</v>
+      </c>
+      <c r="F5" s="779" t="n">
+        <v>64358</v>
+      </c>
+      <c r="G5" s="779">
         <f>E5-F5</f>
         <v/>
       </c>
-      <c r="H5" s="340" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
+      <c r="H5" s="780" t="inlineStr">
+        <is>
+          <t>FORECAST</t>
+        </is>
+      </c>
+      <c r="I5" s="552" t="n"/>
+      <c r="J5" s="552" t="n"/>
     </row>
     <row r="6" ht="19.5" customHeight="1" s="273">
-      <c r="A6" s="290" t="inlineStr">
+      <c r="A6" s="773" t="inlineStr">
         <is>
           <t>Week 3</t>
         </is>
       </c>
-      <c r="B6" s="290" t="inlineStr">
-        <is>
-          <t>Mar 15–21</t>
-        </is>
-      </c>
-      <c r="C6" s="290" t="n">
+      <c r="B6" s="773" t="inlineStr">
+        <is>
+          <t>Apr 15–21</t>
+        </is>
+      </c>
+      <c r="C6" s="773" t="n">
         <v>7</v>
       </c>
-      <c r="D6" s="337" t="inlineStr">
-        <is>
-          <t>Act 46,647 + Fcst 21,043</t>
-        </is>
-      </c>
-      <c r="E6" s="291" t="n">
-        <v>78402</v>
-      </c>
-      <c r="F6" s="291" t="n">
-        <v>30487</v>
-      </c>
-      <c r="G6" s="291">
+      <c r="D6" s="774" t="inlineStr">
+        <is>
+          <t>85,883</t>
+        </is>
+      </c>
+      <c r="E6" s="775" t="n">
+        <v>95072</v>
+      </c>
+      <c r="F6" s="775" t="n">
+        <v>64358</v>
+      </c>
+      <c r="G6" s="775">
         <f>E6-F6</f>
         <v/>
       </c>
-      <c r="H6" s="341" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
+      <c r="H6" s="781" t="inlineStr">
+        <is>
+          <t>FORECAST</t>
+        </is>
+      </c>
+      <c r="I6" s="552" t="n"/>
+      <c r="J6" s="552" t="n"/>
     </row>
     <row r="7" ht="19.5" customHeight="1" s="273">
-      <c r="A7" s="280" t="inlineStr">
+      <c r="A7" s="777" t="inlineStr">
         <is>
           <t>Week 4</t>
         </is>
       </c>
-      <c r="B7" s="280" t="inlineStr">
-        <is>
-          <t>Mar 22–28</t>
-        </is>
-      </c>
-      <c r="C7" s="280" t="n">
+      <c r="B7" s="777" t="inlineStr">
+        <is>
+          <t>Apr 22–28</t>
+        </is>
+      </c>
+      <c r="C7" s="777" t="n">
         <v>7</v>
       </c>
-      <c r="D7" s="339" t="inlineStr">
-        <is>
-          <t>Forecast: 89,929</t>
-        </is>
-      </c>
-      <c r="E7" s="281" t="n">
-        <v>93697</v>
-      </c>
-      <c r="F7" s="281" t="n">
-        <v>30487</v>
-      </c>
-      <c r="G7" s="281">
+      <c r="D7" s="778" t="inlineStr">
+        <is>
+          <t>85,883</t>
+        </is>
+      </c>
+      <c r="E7" s="779" t="n">
+        <v>95072</v>
+      </c>
+      <c r="F7" s="779" t="n">
+        <v>64358</v>
+      </c>
+      <c r="G7" s="779">
         <f>E7-F7</f>
         <v/>
       </c>
-      <c r="H7" s="341" t="inlineStr">
+      <c r="H7" s="781" t="inlineStr">
         <is>
           <t>FORECAST</t>
         </is>
       </c>
+      <c r="I7" s="552" t="n"/>
+      <c r="J7" s="552" t="n"/>
     </row>
     <row r="8" ht="19.5" customHeight="1" s="273">
-      <c r="A8" s="290" t="inlineStr">
+      <c r="A8" s="773" t="inlineStr">
         <is>
           <t>Week 5</t>
         </is>
       </c>
-      <c r="B8" s="290" t="inlineStr">
-        <is>
-          <t>Mar 29–31</t>
-        </is>
-      </c>
-      <c r="C8" s="290" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" s="337" t="inlineStr">
-        <is>
-          <t>Forecast: 38,541</t>
-        </is>
-      </c>
-      <c r="E8" s="291" t="n">
-        <v>40156</v>
-      </c>
-      <c r="F8" s="291" t="n">
-        <v>13066</v>
-      </c>
-      <c r="G8" s="291">
+      <c r="B8" s="773" t="inlineStr">
+        <is>
+          <t>Apr 29–30</t>
+        </is>
+      </c>
+      <c r="C8" s="773" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="774" t="inlineStr">
+        <is>
+          <t>24,538</t>
+        </is>
+      </c>
+      <c r="E8" s="775" t="n">
+        <v>27164</v>
+      </c>
+      <c r="F8" s="775" t="n">
+        <v>18388</v>
+      </c>
+      <c r="G8" s="775">
         <f>E8-F8</f>
         <v/>
       </c>
-      <c r="H8" s="341" t="inlineStr">
+      <c r="H8" s="781" t="inlineStr">
         <is>
           <t>FORECAST</t>
         </is>
       </c>
+      <c r="I8" s="552" t="n"/>
+      <c r="J8" s="552" t="n"/>
     </row>
     <row r="9" ht="19.5" customHeight="1" s="273">
-      <c r="A9" s="317" t="inlineStr">
+      <c r="A9" s="750" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="317" t="inlineStr">
-        <is>
-          <t>Mar 1–31</t>
-        </is>
-      </c>
-      <c r="C9" s="317" t="n">
-        <v>31</v>
-      </c>
-      <c r="D9" s="342" t="inlineStr">
-        <is>
-          <t>351,770</t>
-        </is>
-      </c>
-      <c r="E9" s="343">
+      <c r="B9" s="750" t="inlineStr">
+        <is>
+          <t>Apr 1–30</t>
+        </is>
+      </c>
+      <c r="C9" s="750" t="n">
+        <v>30</v>
+      </c>
+      <c r="D9" s="782" t="inlineStr">
+        <is>
+          <t>368,070</t>
+        </is>
+      </c>
+      <c r="E9" s="783">
         <f>SUM(E4:E8)</f>
         <v/>
       </c>
-      <c r="F9" s="343">
+      <c r="F9" s="783">
         <f>SUM(F4:F8)</f>
         <v/>
       </c>
-      <c r="G9" s="343">
+      <c r="G9" s="783">
         <f>E9-F9</f>
         <v/>
       </c>
-      <c r="H9" s="317" t="n"/>
+      <c r="H9" s="750" t="n"/>
+      <c r="I9" s="552" t="n"/>
+      <c r="J9" s="552" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="552" t="n"/>
+      <c r="B10" s="552" t="n"/>
+      <c r="C10" s="552" t="n"/>
+      <c r="D10" s="552" t="n"/>
+      <c r="E10" s="552" t="n"/>
+      <c r="F10" s="552" t="n"/>
+      <c r="G10" s="552" t="n"/>
+      <c r="H10" s="552" t="n"/>
+      <c r="I10" s="552" t="n"/>
+      <c r="J10" s="552" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="795" t="inlineStr">
+        <is>
+          <t>RUN RATE ASSUMPTIONS:</t>
+        </is>
+      </c>
+      <c r="B11" s="552" t="n"/>
+      <c r="C11" s="552" t="n"/>
+      <c r="D11" s="552" t="n"/>
+      <c r="E11" s="552" t="n"/>
+      <c r="F11" s="552" t="n"/>
+      <c r="G11" s="552" t="n"/>
+      <c r="H11" s="552" t="n"/>
+      <c r="I11" s="552" t="n"/>
+      <c r="J11" s="552" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="786" t="inlineStr">
+        <is>
+          <t>Daily Bbls: 12,269 (Apr 1 actual)  |  Rev/Bbl: $1.107 (Feb-Mar trailing avg)  |  Daily Cost: $9,194 (Jan/Feb actual avg: Jan $10,013/day + Feb $8,375/day)</t>
+        </is>
+      </c>
+      <c r="B12" s="552" t="n"/>
+      <c r="C12" s="552" t="n"/>
+      <c r="D12" s="552" t="n"/>
+      <c r="E12" s="552" t="n"/>
+      <c r="F12" s="552" t="n"/>
+      <c r="G12" s="552" t="n"/>
+      <c r="H12" s="552" t="n"/>
+      <c r="I12" s="552" t="n"/>
+      <c r="J12" s="552" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="786" t="inlineStr">
+        <is>
+          <t>Revenue = Bbls x Rev/Bbl  |  Expenses = Days x Daily Cost  |  Update daily bbls as actuals come in to refresh forecast</t>
+        </is>
+      </c>
+      <c r="B13" s="552" t="n"/>
+      <c r="C13" s="552" t="n"/>
+      <c r="D13" s="552" t="n"/>
+      <c r="E13" s="552" t="n"/>
+      <c r="F13" s="552" t="n"/>
+      <c r="G13" s="552" t="n"/>
+      <c r="H13" s="552" t="n"/>
+      <c r="I13" s="552" t="n"/>
+      <c r="J13" s="552" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="552" t="n"/>
+      <c r="B14" s="552" t="n"/>
+      <c r="C14" s="552" t="n"/>
+      <c r="D14" s="552" t="n"/>
+      <c r="E14" s="552" t="n"/>
+      <c r="F14" s="552" t="n"/>
+      <c r="G14" s="552" t="n"/>
+      <c r="H14" s="552" t="n"/>
+      <c r="I14" s="552" t="n"/>
+      <c r="J14" s="552" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="552" t="n"/>
+      <c r="B15" s="552" t="n"/>
+      <c r="C15" s="552" t="n"/>
+      <c r="D15" s="552" t="n"/>
+      <c r="E15" s="552" t="n"/>
+      <c r="F15" s="552" t="n"/>
+      <c r="G15" s="552" t="n"/>
+      <c r="H15" s="552" t="n"/>
+      <c r="I15" s="552" t="n"/>
+      <c r="J15" s="552" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="552" t="n"/>
+      <c r="B16" s="552" t="n"/>
+      <c r="C16" s="552" t="n"/>
+      <c r="D16" s="552" t="n"/>
+      <c r="E16" s="552" t="n"/>
+      <c r="F16" s="552" t="n"/>
+      <c r="G16" s="552" t="n"/>
+      <c r="H16" s="552" t="n"/>
+      <c r="I16" s="552" t="n"/>
+      <c r="J16" s="552" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="552" t="n"/>
+      <c r="B17" s="552" t="n"/>
+      <c r="C17" s="552" t="n"/>
+      <c r="D17" s="552" t="n"/>
+      <c r="E17" s="552" t="n"/>
+      <c r="F17" s="552" t="n"/>
+      <c r="G17" s="552" t="n"/>
+      <c r="H17" s="552" t="n"/>
+      <c r="I17" s="552" t="n"/>
+      <c r="J17" s="552" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F2"/>
+    <mergeCell ref="A1:H2"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4382,543 +6124,1016 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.71484375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="15" customWidth="1" style="272" min="1" max="1"/>
-    <col width="12" customWidth="1" style="272" min="2" max="2"/>
-    <col width="10" customWidth="1" style="272" min="3" max="3"/>
-    <col width="25" customWidth="1" style="272" min="4" max="4"/>
+    <col width="4" customWidth="1" style="272" min="1" max="1"/>
+    <col width="22" customWidth="1" style="272" min="2" max="2"/>
+    <col width="11" customWidth="1" style="272" min="3" max="3"/>
+    <col width="12" customWidth="1" style="272" min="4" max="4"/>
+    <col width="11" customWidth="1" style="273" min="5" max="5"/>
+    <col width="11" customWidth="1" style="273" min="6" max="6"/>
+    <col width="11" customWidth="1" style="273" min="7" max="7"/>
+    <col width="11" customWidth="1" style="273" min="8" max="8"/>
+    <col width="10" customWidth="1" style="273" min="9" max="9"/>
+    <col width="7" customWidth="1" style="273" min="10" max="10"/>
+    <col width="7" customWidth="1" style="273" min="11" max="11"/>
+    <col width="7" customWidth="1" style="273" min="12" max="12"/>
+    <col width="7" customWidth="1" style="273" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="273">
-      <c r="A1" s="274" t="inlineStr">
-        <is>
-          <t>|  HEADCOUNT BY MONTH &amp; CURRENT ROSTER</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15" customHeight="1" s="273"/>
+      <c r="A1" s="785" t="inlineStr">
+        <is>
+          <t>|  HEADCOUNT &amp; ROSTER  |  Cadiz Terminal</t>
+        </is>
+      </c>
+      <c r="J1" s="552" t="n"/>
+      <c r="K1" s="552" t="n"/>
+      <c r="L1" s="552" t="n"/>
+      <c r="M1" s="552" t="n"/>
+    </row>
+    <row r="2" ht="15" customHeight="1" s="273">
+      <c r="J2" s="552" t="n"/>
+      <c r="K2" s="552" t="n"/>
+      <c r="L2" s="552" t="n"/>
+      <c r="M2" s="552" t="n"/>
+    </row>
     <row r="3" ht="21.75" customHeight="1" s="273">
-      <c r="A3" s="317" t="inlineStr">
+      <c r="A3" s="786" t="inlineStr">
+        <is>
+          <t>Source: QuickBooks Time  |  Corporate salaried (Rob, Tyler, Kelly, Henry) not shown  |  Night shifts spanning midnight = single shift</t>
+        </is>
+      </c>
+      <c r="J3" s="552" t="n"/>
+      <c r="K3" s="552" t="n"/>
+      <c r="L3" s="552" t="n"/>
+      <c r="M3" s="552" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1" s="273">
+      <c r="A4" s="552" t="n"/>
+      <c r="B4" s="552" t="n"/>
+      <c r="C4" s="552" t="n"/>
+      <c r="D4" s="552" t="n"/>
+      <c r="E4" s="552" t="n"/>
+      <c r="F4" s="552" t="n"/>
+      <c r="G4" s="552" t="n"/>
+      <c r="H4" s="552" t="n"/>
+      <c r="I4" s="552" t="n"/>
+      <c r="J4" s="552" t="n"/>
+      <c r="K4" s="552" t="n"/>
+      <c r="L4" s="552" t="n"/>
+      <c r="M4" s="552" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="273">
+      <c r="A5" s="787" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B3" s="317" t="inlineStr">
+      <c r="B5" s="787" t="inlineStr">
+        <is>
+          <t>May 25</t>
+        </is>
+      </c>
+      <c r="C5" s="787" t="inlineStr">
+        <is>
+          <t>Jun 25</t>
+        </is>
+      </c>
+      <c r="D5" s="787" t="inlineStr">
+        <is>
+          <t>Jul 25</t>
+        </is>
+      </c>
+      <c r="E5" s="787" t="inlineStr">
+        <is>
+          <t>Aug 25</t>
+        </is>
+      </c>
+      <c r="F5" s="787" t="inlineStr">
+        <is>
+          <t>Sep 25</t>
+        </is>
+      </c>
+      <c r="G5" s="787" t="inlineStr">
+        <is>
+          <t>Oct 25</t>
+        </is>
+      </c>
+      <c r="H5" s="787" t="inlineStr">
+        <is>
+          <t>Nov 25</t>
+        </is>
+      </c>
+      <c r="I5" s="787" t="inlineStr">
+        <is>
+          <t>Dec 25</t>
+        </is>
+      </c>
+      <c r="J5" s="787" t="inlineStr">
+        <is>
+          <t>Jan 26</t>
+        </is>
+      </c>
+      <c r="K5" s="787" t="inlineStr">
+        <is>
+          <t>Feb 26</t>
+        </is>
+      </c>
+      <c r="L5" s="787" t="inlineStr">
+        <is>
+          <t>Mar 26</t>
+        </is>
+      </c>
+      <c r="M5" s="787" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="273">
+      <c r="A6" s="788" t="inlineStr">
         <is>
           <t>Headcount</t>
         </is>
       </c>
-      <c r="C3" s="317" t="inlineStr">
-        <is>
-          <t>Change</t>
-        </is>
-      </c>
-      <c r="D3" s="317" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1" s="273">
-      <c r="A4" s="290" t="inlineStr">
-        <is>
-          <t>Apr 2025</t>
-        </is>
-      </c>
-      <c r="B4" s="290" t="n">
+      <c r="B6" s="789" t="n">
         <v>4</v>
       </c>
-      <c r="C4" s="290" t="n"/>
-      <c r="D4" s="344" t="inlineStr">
-        <is>
-          <t>Management input</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="273">
-      <c r="A5" s="280" t="inlineStr">
-        <is>
-          <t>May 2025</t>
-        </is>
-      </c>
-      <c r="B5" s="280" t="n">
+      <c r="C6" s="789" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" s="789" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" s="789" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="789" t="n">
+        <v>12</v>
+      </c>
+      <c r="G6" s="789" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" s="789" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" s="789" t="n">
+        <v>12</v>
+      </c>
+      <c r="J6" s="789" t="n">
+        <v>12</v>
+      </c>
+      <c r="K6" s="789" t="n">
+        <v>13</v>
+      </c>
+      <c r="L6" s="789" t="n">
+        <v>15</v>
+      </c>
+      <c r="M6" s="789" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="273">
+      <c r="A7" s="552" t="n"/>
+      <c r="B7" s="552" t="n"/>
+      <c r="C7" s="552" t="n"/>
+      <c r="D7" s="552" t="n"/>
+      <c r="E7" s="552" t="n"/>
+      <c r="F7" s="552" t="n"/>
+      <c r="G7" s="552" t="n"/>
+      <c r="H7" s="552" t="n"/>
+      <c r="I7" s="552" t="n"/>
+      <c r="J7" s="552" t="n"/>
+      <c r="K7" s="552" t="n"/>
+      <c r="L7" s="552" t="n"/>
+      <c r="M7" s="552" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="273">
+      <c r="A8" s="790" t="inlineStr">
+        <is>
+          <t>ACTIVE ROSTER &amp; WEEKLY HOURS</t>
+        </is>
+      </c>
+      <c r="B8" s="552" t="n"/>
+      <c r="C8" s="552" t="n"/>
+      <c r="D8" s="552" t="n"/>
+      <c r="E8" s="552" t="n"/>
+      <c r="F8" s="552" t="n"/>
+      <c r="G8" s="552" t="n"/>
+      <c r="H8" s="552" t="n"/>
+      <c r="I8" s="552" t="n"/>
+      <c r="J8" s="552" t="n"/>
+      <c r="K8" s="552" t="n"/>
+      <c r="L8" s="552" t="n"/>
+      <c r="M8" s="552" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="273">
+      <c r="A9" s="787" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B9" s="787" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C9" s="787" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="D9" s="787" t="inlineStr">
+        <is>
+          <t>WTD
+Mar 30–Apr 2</t>
+        </is>
+      </c>
+      <c r="E9" s="787" t="inlineStr">
+        <is>
+          <t>Wk
+Mar 23–29</t>
+        </is>
+      </c>
+      <c r="F9" s="787" t="inlineStr">
+        <is>
+          <t>Wk
+Mar 16–22</t>
+        </is>
+      </c>
+      <c r="G9" s="787" t="inlineStr">
+        <is>
+          <t>Wk
+Mar 9–15</t>
+        </is>
+      </c>
+      <c r="H9" s="787" t="inlineStr">
+        <is>
+          <t>Wk
+Mar 2–8</t>
+        </is>
+      </c>
+      <c r="I9" s="787" t="inlineStr">
+        <is>
+          <t>Avg
+Hrs/Wk</t>
+        </is>
+      </c>
+      <c r="J9" s="552" t="n"/>
+      <c r="K9" s="552" t="n"/>
+      <c r="L9" s="552" t="n"/>
+      <c r="M9" s="552" t="n"/>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="273">
+      <c r="A10" s="690" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="788" t="inlineStr">
+        <is>
+          <t>Cameron Betz</t>
+        </is>
+      </c>
+      <c r="C10" s="690" t="inlineStr">
+        <is>
+          <t>Supervisor</t>
+        </is>
+      </c>
+      <c r="D10" s="791" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="E10" s="791" t="n">
+        <v>46.53</v>
+      </c>
+      <c r="F10" s="791" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="G10" s="791" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="H10" s="791" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="I10" s="792" t="n">
+        <v>46.60749999999999</v>
+      </c>
+      <c r="J10" s="552" t="n"/>
+      <c r="K10" s="552" t="n"/>
+      <c r="L10" s="552" t="n"/>
+      <c r="M10" s="552" t="n"/>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="273">
+      <c r="A11" s="690" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="788" t="inlineStr">
+        <is>
+          <t>Shawn Osborne Jr.</t>
+        </is>
+      </c>
+      <c r="C11" s="690" t="inlineStr">
+        <is>
+          <t>Supervisor</t>
+        </is>
+      </c>
+      <c r="D11" s="791" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="E11" s="791" t="n">
+        <v>48.47</v>
+      </c>
+      <c r="F11" s="791" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="G11" s="791" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="H11" s="791" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="I11" s="792" t="n">
+        <v>55.9175</v>
+      </c>
+      <c r="J11" s="552" t="n"/>
+      <c r="K11" s="552" t="n"/>
+      <c r="L11" s="552" t="n"/>
+      <c r="M11" s="552" t="n"/>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="273">
+      <c r="A12" s="690" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="788" t="inlineStr">
+        <is>
+          <t>Daniel Hough</t>
+        </is>
+      </c>
+      <c r="C12" s="690" t="inlineStr">
+        <is>
+          <t>Supervisor</t>
+        </is>
+      </c>
+      <c r="D12" s="791" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E12" s="791" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="F12" s="791" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="G12" s="791" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="H12" s="791" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="I12" s="792" t="n">
+        <v>66.65000000000001</v>
+      </c>
+      <c r="J12" s="552" t="n"/>
+      <c r="K12" s="552" t="n"/>
+      <c r="L12" s="552" t="n"/>
+      <c r="M12" s="552" t="n"/>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="273">
+      <c r="A13" s="690" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="345" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="346" t="inlineStr">
-        <is>
-          <t>Management input</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="273">
-      <c r="A6" s="290" t="inlineStr">
-        <is>
-          <t>Jun 2025</t>
-        </is>
-      </c>
-      <c r="B6" s="290" t="n">
+      <c r="B13" s="788" t="inlineStr">
+        <is>
+          <t>Jonathan Williams</t>
+        </is>
+      </c>
+      <c r="C13" s="690" t="inlineStr">
+        <is>
+          <t>Supervisor</t>
+        </is>
+      </c>
+      <c r="D13" s="791" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="E13" s="791" t="n">
+        <v>60.58</v>
+      </c>
+      <c r="F13" s="791" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="G13" s="791" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="H13" s="791" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="I13" s="792" t="n">
+        <v>64.17</v>
+      </c>
+      <c r="J13" s="552" t="n"/>
+      <c r="K13" s="552" t="n"/>
+      <c r="L13" s="552" t="n"/>
+      <c r="M13" s="552" t="n"/>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="273">
+      <c r="A14" s="690" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="788" t="inlineStr">
+        <is>
+          <t>Shane Young</t>
+        </is>
+      </c>
+      <c r="C14" s="690" t="inlineStr">
+        <is>
+          <t>Loader</t>
+        </is>
+      </c>
+      <c r="D14" s="690" t="n"/>
+      <c r="E14" s="791" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="F14" s="791" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="G14" s="791" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="H14" s="791" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="I14" s="792" t="n">
+        <v>58.55</v>
+      </c>
+      <c r="J14" s="552" t="n"/>
+      <c r="K14" s="552" t="n"/>
+      <c r="L14" s="552" t="n"/>
+      <c r="M14" s="552" t="n"/>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="273">
+      <c r="A15" s="690" t="n">
         <v>6</v>
       </c>
-      <c r="C6" s="347" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" s="344" t="inlineStr">
-        <is>
-          <t>Management input</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="273">
-      <c r="A7" s="280" t="inlineStr">
-        <is>
-          <t>Jul 2025</t>
-        </is>
-      </c>
-      <c r="B7" s="280" t="n">
+      <c r="B15" s="788" t="inlineStr">
+        <is>
+          <t>William Glover</t>
+        </is>
+      </c>
+      <c r="C15" s="690" t="inlineStr">
+        <is>
+          <t>Loader</t>
+        </is>
+      </c>
+      <c r="D15" s="690" t="n"/>
+      <c r="E15" s="791" t="n">
+        <v>61.82</v>
+      </c>
+      <c r="F15" s="791" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="G15" s="791" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="H15" s="791" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="I15" s="792" t="n">
+        <v>52.45500000000001</v>
+      </c>
+      <c r="J15" s="552" t="n"/>
+      <c r="K15" s="552" t="n"/>
+      <c r="L15" s="552" t="n"/>
+      <c r="M15" s="552" t="n"/>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="273">
+      <c r="A16" s="690" t="n">
+        <v>7</v>
+      </c>
+      <c r="B16" s="788" t="inlineStr">
+        <is>
+          <t>Bryan Deoss</t>
+        </is>
+      </c>
+      <c r="C16" s="690" t="inlineStr">
+        <is>
+          <t>Loader</t>
+        </is>
+      </c>
+      <c r="D16" s="791" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" s="791" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="F16" s="791" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="G16" s="791" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="H16" s="791" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="I16" s="792" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="J16" s="552" t="n"/>
+      <c r="K16" s="552" t="n"/>
+      <c r="L16" s="552" t="n"/>
+      <c r="M16" s="552" t="n"/>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="273">
+      <c r="A17" s="690" t="n">
         <v>8</v>
       </c>
-      <c r="C7" s="348" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" s="346" t="inlineStr">
-        <is>
-          <t>Management input</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="273">
-      <c r="A8" s="290" t="inlineStr">
-        <is>
-          <t>Aug 2025</t>
-        </is>
-      </c>
-      <c r="B8" s="290" t="n">
+      <c r="B17" s="788" t="inlineStr">
+        <is>
+          <t>Austin Tredway</t>
+        </is>
+      </c>
+      <c r="C17" s="690" t="inlineStr">
+        <is>
+          <t>Loader</t>
+        </is>
+      </c>
+      <c r="D17" s="791" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="E17" s="791" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="F17" s="791" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="G17" s="791" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="H17" s="791" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="I17" s="792" t="n">
+        <v>54.625</v>
+      </c>
+      <c r="J17" s="552" t="n"/>
+      <c r="K17" s="552" t="n"/>
+      <c r="L17" s="552" t="n"/>
+      <c r="M17" s="552" t="n"/>
+    </row>
+    <row r="18" ht="15" customHeight="1" s="273">
+      <c r="A18" s="690" t="n">
+        <v>9</v>
+      </c>
+      <c r="B18" s="788" t="inlineStr">
+        <is>
+          <t>Jacob Diloreto</t>
+        </is>
+      </c>
+      <c r="C18" s="690" t="inlineStr">
+        <is>
+          <t>Loader</t>
+        </is>
+      </c>
+      <c r="D18" s="791" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E18" s="791" t="n">
+        <v>62.52</v>
+      </c>
+      <c r="F18" s="791" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="G18" s="791" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="H18" s="791" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="I18" s="792" t="n">
+        <v>65.30500000000001</v>
+      </c>
+      <c r="J18" s="552" t="n"/>
+      <c r="K18" s="552" t="n"/>
+      <c r="L18" s="552" t="n"/>
+      <c r="M18" s="552" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="273">
+      <c r="A19" s="690" t="n">
         <v>10</v>
       </c>
-      <c r="C8" s="347" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" s="344" t="inlineStr">
-        <is>
-          <t>Management input</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="273">
-      <c r="A9" s="280" t="inlineStr">
-        <is>
-          <t>Sep 2025</t>
-        </is>
-      </c>
-      <c r="B9" s="280" t="n">
+      <c r="B19" s="788" t="inlineStr">
+        <is>
+          <t>Dustin Fletcher</t>
+        </is>
+      </c>
+      <c r="C19" s="690" t="inlineStr">
+        <is>
+          <t>Loader</t>
+        </is>
+      </c>
+      <c r="D19" s="791" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E19" s="791" t="n">
+        <v>67.65000000000001</v>
+      </c>
+      <c r="F19" s="791" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="G19" s="791" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="H19" s="791" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="I19" s="792" t="n">
+        <v>64.91250000000001</v>
+      </c>
+      <c r="J19" s="552" t="n"/>
+      <c r="K19" s="552" t="n"/>
+      <c r="L19" s="552" t="n"/>
+      <c r="M19" s="552" t="n"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" s="273">
+      <c r="A20" s="690" t="n">
+        <v>11</v>
+      </c>
+      <c r="B20" s="788" t="inlineStr">
+        <is>
+          <t>Jared Wright</t>
+        </is>
+      </c>
+      <c r="C20" s="690" t="inlineStr">
+        <is>
+          <t>Loader</t>
+        </is>
+      </c>
+      <c r="D20" s="791" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E20" s="791" t="n">
+        <v>44.62</v>
+      </c>
+      <c r="F20" s="791" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="G20" s="791" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="H20" s="791" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="I20" s="792" t="n">
+        <v>48.855</v>
+      </c>
+      <c r="J20" s="552" t="n"/>
+      <c r="K20" s="552" t="n"/>
+      <c r="L20" s="552" t="n"/>
+      <c r="M20" s="552" t="n"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" s="273">
+      <c r="A21" s="690" t="n">
         <v>12</v>
       </c>
-      <c r="C9" s="348" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" s="346" t="inlineStr">
-        <is>
-          <t>Management input</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="273">
-      <c r="A10" s="290" t="inlineStr">
-        <is>
-          <t>Oct 2025</t>
-        </is>
-      </c>
-      <c r="B10" s="290" t="n">
-        <v>12</v>
-      </c>
-      <c r="C10" s="349" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="344" t="inlineStr">
-        <is>
-          <t>Management input</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="273">
-      <c r="A11" s="280" t="inlineStr">
-        <is>
-          <t>Nov 2025</t>
-        </is>
-      </c>
-      <c r="B11" s="280" t="n">
-        <v>12</v>
-      </c>
-      <c r="C11" s="345" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="346" t="inlineStr">
-        <is>
-          <t>Payroll PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="273">
-      <c r="A12" s="290" t="inlineStr">
-        <is>
-          <t>Dec 2025</t>
-        </is>
-      </c>
-      <c r="B12" s="290" t="n">
-        <v>12</v>
-      </c>
-      <c r="C12" s="349" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="344" t="inlineStr">
-        <is>
-          <t>Payroll PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="273">
-      <c r="A13" s="280" t="inlineStr">
-        <is>
-          <t>Jan 2026</t>
-        </is>
-      </c>
-      <c r="B13" s="280" t="n">
-        <v>12</v>
-      </c>
-      <c r="C13" s="345" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="346" t="inlineStr">
-        <is>
-          <t>Payroll PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="273">
-      <c r="A14" s="290" t="inlineStr">
-        <is>
-          <t>Feb 2026</t>
-        </is>
-      </c>
-      <c r="B14" s="290" t="n">
+      <c r="B21" s="788" t="inlineStr">
+        <is>
+          <t>Nathaniel Medel</t>
+        </is>
+      </c>
+      <c r="C21" s="690" t="inlineStr">
+        <is>
+          <t>Loader</t>
+        </is>
+      </c>
+      <c r="D21" s="791" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E21" s="791" t="n">
+        <v>60.88</v>
+      </c>
+      <c r="F21" s="791" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="G21" s="791" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="H21" s="791" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="I21" s="792" t="n">
+        <v>63.69500000000001</v>
+      </c>
+      <c r="J21" s="552" t="n"/>
+      <c r="K21" s="552" t="n"/>
+      <c r="L21" s="552" t="n"/>
+      <c r="M21" s="552" t="n"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1" s="273">
+      <c r="A22" s="690" t="n">
         <v>13</v>
       </c>
-      <c r="C14" s="347" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="344" t="inlineStr">
-        <is>
-          <t>Payroll PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="273">
-      <c r="A15" s="280" t="inlineStr">
-        <is>
-          <t>Mar 2026</t>
-        </is>
-      </c>
-      <c r="B15" s="280" t="n">
+      <c r="B22" s="788" t="inlineStr">
+        <is>
+          <t>Gregory Bates</t>
+        </is>
+      </c>
+      <c r="C22" s="690" t="inlineStr">
+        <is>
+          <t>Loader</t>
+        </is>
+      </c>
+      <c r="D22" s="690" t="n"/>
+      <c r="E22" s="791" t="n">
+        <v>48.42</v>
+      </c>
+      <c r="F22" s="791" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="G22" s="791" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="H22" s="690" t="n"/>
+      <c r="I22" s="792" t="n">
+        <v>60.77333333333333</v>
+      </c>
+      <c r="J22" s="552" t="n"/>
+      <c r="K22" s="552" t="n"/>
+      <c r="L22" s="552" t="n"/>
+      <c r="M22" s="552" t="n"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="273">
+      <c r="A23" s="690" t="n">
+        <v>14</v>
+      </c>
+      <c r="B23" s="788" t="inlineStr">
+        <is>
+          <t>Shawn Osborne Sr. (OZ)</t>
+        </is>
+      </c>
+      <c r="C23" s="690" t="inlineStr">
+        <is>
+          <t>Loader</t>
+        </is>
+      </c>
+      <c r="D23" s="791" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="E23" s="791" t="n">
+        <v>48.23</v>
+      </c>
+      <c r="F23" s="791" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="G23" s="791" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="H23" s="791" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="I23" s="792" t="n">
+        <v>55.9575</v>
+      </c>
+      <c r="J23" s="552" t="n"/>
+      <c r="K23" s="552" t="n"/>
+      <c r="L23" s="552" t="n"/>
+      <c r="M23" s="552" t="n"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" s="273">
+      <c r="A24" s="690" t="n">
         <v>15</v>
       </c>
-      <c r="C15" s="348" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" s="346" t="inlineStr">
-        <is>
-          <t>Payroll CSV + Roster (updated Mar 22)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="273"/>
-    <row r="17" ht="15" customHeight="1" s="273"/>
-    <row r="18" ht="15" customHeight="1" s="273">
-      <c r="A18" s="350" t="inlineStr">
-        <is>
-          <t>CURRENT ROSTER  –  CADIZ TERMINAL  (Mar 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15.75" customHeight="1" s="273">
-      <c r="A19" s="317" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B19" s="317" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C19" s="317" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="D19" s="317" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15.75" customHeight="1" s="273">
-      <c r="A20" s="351" t="n">
-        <v>1</v>
-      </c>
-      <c r="B20" s="352" t="inlineStr">
-        <is>
-          <t>Cam Betz</t>
-        </is>
-      </c>
-      <c r="C20" s="351" t="inlineStr">
-        <is>
-          <t>Supervisor</t>
-        </is>
-      </c>
-      <c r="D20" s="352" t="n"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1" s="273">
-      <c r="A21" s="351" t="n">
-        <v>2</v>
-      </c>
-      <c r="B21" s="352" t="inlineStr">
-        <is>
-          <t>Shawn Osborne Jr.</t>
-        </is>
-      </c>
-      <c r="C21" s="351" t="inlineStr">
-        <is>
-          <t>Supervisor</t>
-        </is>
-      </c>
-      <c r="D21" s="352" t="n"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1" s="273">
-      <c r="A22" s="351" t="n">
-        <v>3</v>
-      </c>
-      <c r="B22" s="352" t="inlineStr">
-        <is>
-          <t>Daniel Hough</t>
-        </is>
-      </c>
-      <c r="C22" s="351" t="inlineStr">
-        <is>
-          <t>Supervisor</t>
-        </is>
-      </c>
-      <c r="D22" s="352" t="n"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1" s="273">
-      <c r="A23" s="351" t="n">
-        <v>4</v>
-      </c>
-      <c r="B23" s="352" t="inlineStr">
-        <is>
-          <t>Jonathan Williams</t>
-        </is>
-      </c>
-      <c r="C23" s="351" t="inlineStr">
-        <is>
-          <t>Supervisor</t>
-        </is>
-      </c>
-      <c r="D23" s="352" t="n"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1" s="273">
-      <c r="A24" s="290" t="n">
-        <v>5</v>
-      </c>
-      <c r="B24" s="344" t="inlineStr">
-        <is>
-          <t>Shane Young</t>
-        </is>
-      </c>
-      <c r="C24" s="290" t="inlineStr">
+      <c r="B24" s="788" t="inlineStr">
+        <is>
+          <t>Christopher Wright</t>
+        </is>
+      </c>
+      <c r="C24" s="690" t="inlineStr">
         <is>
           <t>Loader</t>
         </is>
       </c>
-      <c r="D24" s="344" t="n"/>
+      <c r="D24" s="791" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E24" s="690" t="n"/>
+      <c r="F24" s="690" t="n"/>
+      <c r="G24" s="690" t="n"/>
+      <c r="H24" s="690" t="n"/>
+      <c r="I24" s="791" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J24" s="552" t="n"/>
+      <c r="K24" s="552" t="n"/>
+      <c r="L24" s="552" t="n"/>
+      <c r="M24" s="552" t="n"/>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="273">
-      <c r="A25" s="280" t="n">
-        <v>6</v>
-      </c>
-      <c r="B25" s="346" t="inlineStr">
-        <is>
-          <t>Billy Glover</t>
-        </is>
-      </c>
-      <c r="C25" s="280" t="inlineStr">
-        <is>
-          <t>Loader</t>
-        </is>
-      </c>
-      <c r="D25" s="346" t="n"/>
+      <c r="A25" s="793" t="n"/>
+      <c r="B25" s="703" t="inlineStr">
+        <is>
+          <t>TOTALS</t>
+        </is>
+      </c>
+      <c r="C25" s="793" t="n"/>
+      <c r="D25" s="794">
+        <f>SUM(D10:D24)</f>
+        <v/>
+      </c>
+      <c r="E25" s="794">
+        <f>SUM(E10:E24)</f>
+        <v/>
+      </c>
+      <c r="F25" s="794">
+        <f>SUM(F10:F24)</f>
+        <v/>
+      </c>
+      <c r="G25" s="794">
+        <f>SUM(G10:G24)</f>
+        <v/>
+      </c>
+      <c r="H25" s="794">
+        <f>SUM(H10:H24)</f>
+        <v/>
+      </c>
+      <c r="I25" s="794">
+        <f>AVERAGE(I10:I24)</f>
+        <v/>
+      </c>
+      <c r="J25" s="552" t="n"/>
+      <c r="K25" s="552" t="n"/>
+      <c r="L25" s="552" t="n"/>
+      <c r="M25" s="552" t="n"/>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="273">
-      <c r="A26" s="280" t="n">
-        <v>7</v>
-      </c>
-      <c r="B26" s="346" t="inlineStr">
-        <is>
-          <t>Bryan Deoss</t>
-        </is>
-      </c>
-      <c r="C26" s="280" t="inlineStr">
-        <is>
-          <t>Loader</t>
-        </is>
-      </c>
-      <c r="D26" s="346" t="n"/>
+      <c r="A26" s="552" t="n"/>
+      <c r="B26" s="552" t="n"/>
+      <c r="C26" s="552" t="n"/>
+      <c r="D26" s="552" t="n"/>
+      <c r="E26" s="552" t="n"/>
+      <c r="F26" s="552" t="n"/>
+      <c r="G26" s="552" t="n"/>
+      <c r="H26" s="552" t="n"/>
+      <c r="I26" s="552" t="n"/>
+      <c r="J26" s="552" t="n"/>
+      <c r="K26" s="552" t="n"/>
+      <c r="L26" s="552" t="n"/>
+      <c r="M26" s="552" t="n"/>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="273">
-      <c r="A27" s="290" t="n">
-        <v>8</v>
-      </c>
-      <c r="B27" s="344" t="inlineStr">
-        <is>
-          <t>Austin Treadway</t>
-        </is>
-      </c>
-      <c r="C27" s="290" t="inlineStr">
-        <is>
-          <t>Loader</t>
-        </is>
-      </c>
-      <c r="D27" s="344" t="n"/>
+      <c r="A27" s="786" t="inlineStr">
+        <is>
+          <t>WTD = Week to date (partial — day shift still active Apr 2). Avg based on 4 full weeks only.</t>
+        </is>
+      </c>
+      <c r="B27" s="552" t="n"/>
+      <c r="C27" s="552" t="n"/>
+      <c r="D27" s="552" t="n"/>
+      <c r="E27" s="552" t="n"/>
+      <c r="F27" s="552" t="n"/>
+      <c r="G27" s="552" t="n"/>
+      <c r="H27" s="552" t="n"/>
+      <c r="I27" s="552" t="n"/>
+      <c r="J27" s="552" t="n"/>
+      <c r="K27" s="552" t="n"/>
+      <c r="L27" s="552" t="n"/>
+      <c r="M27" s="552" t="n"/>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="273">
-      <c r="A28" s="280" t="n">
-        <v>9</v>
-      </c>
-      <c r="B28" s="346" t="inlineStr">
-        <is>
-          <t>Jacob Diloreto</t>
-        </is>
-      </c>
-      <c r="C28" s="280" t="inlineStr">
-        <is>
-          <t>Loader</t>
-        </is>
-      </c>
-      <c r="D28" s="346" t="n"/>
+      <c r="A28" s="786" t="inlineStr">
+        <is>
+          <t>Two Shawn Osborn accounts in QB Time (gosborn20 = Jr, osbournshawn25 = Sr/OZ). Mar 9–15 separated by account.</t>
+        </is>
+      </c>
+      <c r="B28" s="552" t="n"/>
+      <c r="C28" s="552" t="n"/>
+      <c r="D28" s="552" t="n"/>
+      <c r="E28" s="552" t="n"/>
+      <c r="F28" s="552" t="n"/>
+      <c r="G28" s="552" t="n"/>
+      <c r="H28" s="552" t="n"/>
+      <c r="I28" s="552" t="n"/>
+      <c r="J28" s="552" t="n"/>
+      <c r="K28" s="552" t="n"/>
+      <c r="L28" s="552" t="n"/>
+      <c r="M28" s="552" t="n"/>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="273">
-      <c r="A29" s="290" t="n">
-        <v>10</v>
-      </c>
-      <c r="B29" s="344" t="inlineStr">
-        <is>
-          <t>Dustin Fletcher</t>
-        </is>
-      </c>
-      <c r="C29" s="290" t="inlineStr">
-        <is>
-          <t>Loader</t>
-        </is>
-      </c>
-      <c r="D29" s="344" t="n"/>
+      <c r="A29" s="786" t="inlineStr">
+        <is>
+          <t>Christopher Wright = new hire, started Mon Mar 30. Thomas Carney no longer employed. Net HC = 15.</t>
+        </is>
+      </c>
+      <c r="B29" s="552" t="n"/>
+      <c r="C29" s="552" t="n"/>
+      <c r="D29" s="552" t="n"/>
+      <c r="E29" s="552" t="n"/>
+      <c r="F29" s="552" t="n"/>
+      <c r="G29" s="552" t="n"/>
+      <c r="H29" s="552" t="n"/>
+      <c r="I29" s="552" t="n"/>
+      <c r="J29" s="552" t="n"/>
+      <c r="K29" s="552" t="n"/>
+      <c r="L29" s="552" t="n"/>
+      <c r="M29" s="552" t="n"/>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="273">
-      <c r="A30" s="280" t="n">
-        <v>11</v>
-      </c>
-      <c r="B30" s="346" t="inlineStr">
-        <is>
-          <t>Jared Wright</t>
-        </is>
-      </c>
-      <c r="C30" s="280" t="inlineStr">
-        <is>
-          <t>Loader</t>
-        </is>
-      </c>
-      <c r="D30" s="346" t="n"/>
+      <c r="A30" s="552" t="n"/>
+      <c r="B30" s="552" t="n"/>
+      <c r="C30" s="552" t="n"/>
+      <c r="D30" s="552" t="n"/>
+      <c r="E30" s="552" t="n"/>
+      <c r="F30" s="552" t="n"/>
+      <c r="G30" s="552" t="n"/>
+      <c r="H30" s="552" t="n"/>
+      <c r="I30" s="552" t="n"/>
+      <c r="J30" s="552" t="n"/>
+      <c r="K30" s="552" t="n"/>
+      <c r="L30" s="552" t="n"/>
+      <c r="M30" s="552" t="n"/>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="273">
-      <c r="A31" s="290" t="n">
-        <v>12</v>
-      </c>
-      <c r="B31" s="344" t="inlineStr">
-        <is>
-          <t>Nate Medel</t>
-        </is>
-      </c>
-      <c r="C31" s="290" t="inlineStr">
-        <is>
-          <t>Loader</t>
-        </is>
-      </c>
-      <c r="D31" s="344" t="n"/>
+      <c r="A31" s="552" t="n"/>
+      <c r="B31" s="552" t="n"/>
+      <c r="C31" s="552" t="n"/>
+      <c r="D31" s="552" t="n"/>
+      <c r="E31" s="552" t="n"/>
+      <c r="F31" s="552" t="n"/>
+      <c r="G31" s="552" t="n"/>
+      <c r="H31" s="552" t="n"/>
+      <c r="I31" s="552" t="n"/>
+      <c r="J31" s="552" t="n"/>
+      <c r="K31" s="552" t="n"/>
+      <c r="L31" s="552" t="n"/>
+      <c r="M31" s="552" t="n"/>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="273">
-      <c r="A32" s="280" t="n">
-        <v>13</v>
-      </c>
-      <c r="B32" s="346" t="inlineStr">
-        <is>
-          <t>Greg Bates</t>
-        </is>
-      </c>
-      <c r="C32" s="280" t="inlineStr">
-        <is>
-          <t>Loader</t>
-        </is>
-      </c>
-      <c r="D32" s="346" t="n"/>
+      <c r="A32" s="552" t="n"/>
+      <c r="B32" s="552" t="n"/>
+      <c r="C32" s="552" t="n"/>
+      <c r="D32" s="552" t="n"/>
+      <c r="E32" s="552" t="n"/>
+      <c r="F32" s="552" t="n"/>
+      <c r="G32" s="552" t="n"/>
+      <c r="H32" s="552" t="n"/>
+      <c r="I32" s="552" t="n"/>
+      <c r="J32" s="552" t="n"/>
+      <c r="K32" s="552" t="n"/>
+      <c r="L32" s="552" t="n"/>
+      <c r="M32" s="552" t="n"/>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="273">
-      <c r="A33" s="290" t="n">
-        <v>14</v>
-      </c>
-      <c r="B33" s="344" t="inlineStr">
-        <is>
-          <t>Tom Carney</t>
-        </is>
-      </c>
-      <c r="C33" s="290" t="inlineStr">
-        <is>
-          <t>Loader</t>
-        </is>
-      </c>
-      <c r="D33" s="344" t="n"/>
+      <c r="A33" s="552" t="n"/>
+      <c r="B33" s="552" t="n"/>
+      <c r="C33" s="552" t="n"/>
+      <c r="D33" s="552" t="n"/>
+      <c r="E33" s="552" t="n"/>
+      <c r="F33" s="552" t="n"/>
+      <c r="G33" s="552" t="n"/>
+      <c r="H33" s="552" t="n"/>
+      <c r="I33" s="552" t="n"/>
+      <c r="J33" s="552" t="n"/>
+      <c r="K33" s="552" t="n"/>
+      <c r="L33" s="552" t="n"/>
+      <c r="M33" s="552" t="n"/>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="273">
-      <c r="A34" s="280" t="n">
-        <v>15</v>
-      </c>
-      <c r="B34" s="346" t="inlineStr">
-        <is>
-          <t>Shawn Osborne Sr. (OZ)</t>
-        </is>
-      </c>
-      <c r="C34" s="280" t="inlineStr">
-        <is>
-          <t>Loader</t>
-        </is>
-      </c>
-      <c r="D34" s="346" t="inlineStr">
-        <is>
-          <t>Father of Shawn Jr.; started Feb 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1" s="273"/>
+      <c r="A34" s="552" t="n"/>
+      <c r="B34" s="552" t="n"/>
+      <c r="C34" s="552" t="n"/>
+      <c r="D34" s="552" t="n"/>
+      <c r="E34" s="552" t="n"/>
+      <c r="F34" s="552" t="n"/>
+      <c r="G34" s="552" t="n"/>
+      <c r="H34" s="552" t="n"/>
+      <c r="I34" s="552" t="n"/>
+      <c r="J34" s="552" t="n"/>
+      <c r="K34" s="552" t="n"/>
+      <c r="L34" s="552" t="n"/>
+      <c r="M34" s="552" t="n"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1" s="273">
+      <c r="A35" s="552" t="n"/>
+      <c r="B35" s="552" t="n"/>
+      <c r="C35" s="552" t="n"/>
+      <c r="D35" s="552" t="n"/>
+      <c r="E35" s="552" t="n"/>
+      <c r="F35" s="552" t="n"/>
+      <c r="G35" s="552" t="n"/>
+      <c r="H35" s="552" t="n"/>
+      <c r="I35" s="552" t="n"/>
+      <c r="J35" s="552" t="n"/>
+      <c r="K35" s="552" t="n"/>
+      <c r="L35" s="552" t="n"/>
+      <c r="M35" s="552" t="n"/>
+    </row>
     <row r="36" ht="15.75" customHeight="1" s="273"/>
     <row r="37" ht="15.75" customHeight="1" s="273"/>
     <row r="38" ht="15.75" customHeight="1" s="273"/>
     <row r="39" ht="15.75" customHeight="1" s="273"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A1:I2"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -5444,42 +7659,42 @@
     <row r="15" ht="15" customHeight="1" s="273">
       <c r="A15" s="370" t="inlineStr">
         <is>
-          <t>Mar 2026†</t>
+          <t>April 2026†</t>
         </is>
       </c>
       <c r="B15" s="371" t="n">
-        <v>744</v>
+        <v>720</v>
       </c>
       <c r="C15" s="363" t="n">
-        <v>256</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="D15" s="363" t="n">
-        <v>488</v>
+        <v>11.38</v>
       </c>
       <c r="E15" s="364" t="n">
-        <v>0.344</v>
+        <v>0.458</v>
       </c>
       <c r="F15" s="365" t="n">
-        <v>263.7</v>
+        <v>8.23</v>
       </c>
       <c r="G15" s="365" t="n">
-        <v>480.3</v>
+        <v>12.77</v>
       </c>
       <c r="H15" s="366" t="n">
-        <v>0.354</v>
+        <v>0.392</v>
       </c>
       <c r="I15" s="367" t="n">
-        <v>196.22</v>
+        <v>9.1</v>
       </c>
       <c r="J15" s="367" t="n">
-        <v>547.78</v>
+        <v>11.9</v>
       </c>
       <c r="K15" s="368" t="n">
-        <v>0.264</v>
+        <v>0.433</v>
       </c>
       <c r="L15" s="372" t="inlineStr">
         <is>
-          <t>All 3 pumps active · Partial month thru Mar 30</t>
+          <t>All 3 pumps active — Partial month thru Apr 1</t>
         </is>
       </c>
     </row>
@@ -13281,36 +15496,70 @@
       <c r="J10" s="455" t="n"/>
     </row>
     <row r="11" ht="15.75" customHeight="1" s="273">
-      <c r="A11" s="461" t="inlineStr">
+      <c r="A11" s="588" t="inlineStr">
+        <is>
+          <t>1st Choice</t>
+        </is>
+      </c>
+      <c r="B11" s="589" t="inlineStr">
+        <is>
+          <t>04/02/26</t>
+        </is>
+      </c>
+      <c r="C11" s="590" t="n">
+        <v>250.6</v>
+      </c>
+      <c r="D11" s="591" t="n">
+        <v>4.1415</v>
+      </c>
+      <c r="E11" s="592" t="n">
+        <v>1037.85</v>
+      </c>
+      <c r="F11" s="593" t="n">
+        <v>75</v>
+      </c>
+      <c r="G11" s="593" t="n">
+        <v>1112.85</v>
+      </c>
+      <c r="H11" s="588" t="n">
+        <v>28</v>
+      </c>
+      <c r="I11" s="461" t="n"/>
+      <c r="J11" s="594" t="inlineStr">
+        <is>
+          <t>1st Choice Energy (not Heritage) — Cadiz site delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="7.5" customHeight="1" s="273">
+      <c r="A12" s="595" t="inlineStr">
         <is>
           <t>TOTALS / AVERAGES</t>
         </is>
       </c>
-      <c r="B11" s="355" t="n"/>
-      <c r="C11" s="462" t="n">
+      <c r="C12" s="596" t="n">
         <v>1721.8</v>
       </c>
-      <c r="D11" s="463" t="n">
+      <c r="D12" s="597" t="n">
         <v>2.9828</v>
       </c>
-      <c r="E11" s="464" t="n">
+      <c r="E12" s="598" t="n">
         <v>5135.83</v>
       </c>
-      <c r="F11" s="464" t="n">
+      <c r="F12" s="598" t="n">
         <v>380.6</v>
       </c>
-      <c r="G11" s="464" t="n">
+      <c r="G12" s="598" t="n">
         <v>5516.43</v>
       </c>
-      <c r="H11" s="461" t="inlineStr">
+      <c r="H12" s="595" t="inlineStr">
         <is>
           <t>28 days</t>
         </is>
       </c>
-      <c r="I11" s="461" t="n"/>
-      <c r="J11" s="461" t="n"/>
-    </row>
-    <row r="12" ht="7.5" customHeight="1" s="273"/>
+      <c r="I12" s="595" t="n"/>
+      <c r="J12" s="595" t="n"/>
+    </row>
     <row r="13" ht="15.75" customHeight="1" s="273">
       <c r="A13" s="449" t="inlineStr">
         <is>
@@ -13863,10 +16112,9 @@
       <c r="J37" s="451" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A27:J27"/>
-    <mergeCell ref="A11:B11"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A19:J19"/>
     <mergeCell ref="A2:J2"/>
@@ -13885,12 +16133,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M85"/>
+  <dimension ref="A1:M94"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.71484375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="22" customWidth="1" style="272" min="1" max="1"/>
-    <col width="8" customWidth="1" style="272" min="2" max="2"/>
-    <col width="9" customWidth="1" style="272" min="3" max="10"/>
+    <col width="14" customWidth="1" style="272" min="1" max="1"/>
+    <col width="14" customWidth="1" style="272" min="2" max="2"/>
+    <col width="14" customWidth="1" style="272" min="3" max="10"/>
+    <col width="14" customWidth="1" style="273" min="4" max="4"/>
+    <col width="14" customWidth="1" style="273" min="5" max="5"/>
+    <col width="14" customWidth="1" style="273" min="6" max="6"/>
+    <col width="14" customWidth="1" style="273" min="7" max="7"/>
+    <col width="14" customWidth="1" style="273" min="8" max="8"/>
+    <col width="14" customWidth="1" style="273" min="9" max="9"/>
     <col width="12" customWidth="1" style="272" min="11" max="13"/>
   </cols>
   <sheetData>
@@ -14623,9 +16877,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M18" s="426" t="inlineStr">
-        <is>
-          <t>* Partial month thru Mar 16 — est rev lost n/a</t>
+      <c r="M18" s="599" t="inlineStr">
+        <is>
+          <t>Full month — 31 days at 10,312 bbls/day</t>
         </is>
       </c>
     </row>
@@ -16366,6 +18620,191 @@
       <c r="K85" s="354" t="n"/>
       <c r="L85" s="354" t="n"/>
       <c r="M85" s="354" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="600" t="inlineStr">
+        <is>
+          <t>REVENUE &amp; COST PER LOADER</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="574" t="inlineStr">
+        <is>
+          <t>Corporate salaried (Rob, Tyler, Kelly, Henry) = fixed cost excluded  |  Field crew = hourly</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="575" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B90" s="575" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C90" s="575" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="D90" s="575" t="inlineStr">
+        <is>
+          <t>Corp Salary</t>
+        </is>
+      </c>
+      <c r="E90" s="575" t="inlineStr">
+        <is>
+          <t>Field Cost</t>
+        </is>
+      </c>
+      <c r="F90" s="575" t="inlineStr">
+        <is>
+          <t>Loaders</t>
+        </is>
+      </c>
+      <c r="G90" s="575" t="inlineStr">
+        <is>
+          <t>Rev/Loader</t>
+        </is>
+      </c>
+      <c r="H90" s="575" t="inlineStr">
+        <is>
+          <t>Cost/Loader</t>
+        </is>
+      </c>
+      <c r="I90" s="575" t="inlineStr">
+        <is>
+          <t>Margin/Loader</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="601" t="inlineStr">
+        <is>
+          <t>Apr 2026†</t>
+        </is>
+      </c>
+      <c r="B91" s="557" t="n">
+        <v>407307</v>
+      </c>
+      <c r="C91" s="557" t="n">
+        <v>255376</v>
+      </c>
+      <c r="D91" s="557" t="n">
+        <v>30497</v>
+      </c>
+      <c r="E91" s="557" t="n">
+        <v>224879</v>
+      </c>
+      <c r="F91" s="557" t="n">
+        <v>15</v>
+      </c>
+      <c r="G91" s="602" t="n">
+        <v>27154</v>
+      </c>
+      <c r="H91" s="557" t="n">
+        <v>14992</v>
+      </c>
+      <c r="I91" s="603" t="n">
+        <v>12162</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="604" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="B92" s="559" t="n">
+        <v>356011</v>
+      </c>
+      <c r="C92" s="559" t="n">
+        <v>244584</v>
+      </c>
+      <c r="D92" s="559" t="n">
+        <v>27955</v>
+      </c>
+      <c r="E92" s="559" t="n">
+        <v>216629</v>
+      </c>
+      <c r="F92" s="559" t="n">
+        <v>15</v>
+      </c>
+      <c r="G92" s="605" t="n">
+        <v>23734</v>
+      </c>
+      <c r="H92" s="559" t="n">
+        <v>14442</v>
+      </c>
+      <c r="I92" s="606" t="n">
+        <v>9292</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="607" t="inlineStr">
+        <is>
+          <t>Feb 2026</t>
+        </is>
+      </c>
+      <c r="B93" s="558" t="n">
+        <v>344761</v>
+      </c>
+      <c r="C93" s="558" t="n">
+        <v>234498</v>
+      </c>
+      <c r="D93" s="558" t="n">
+        <v>27955</v>
+      </c>
+      <c r="E93" s="558" t="n">
+        <v>206543</v>
+      </c>
+      <c r="F93" s="558" t="n">
+        <v>13</v>
+      </c>
+      <c r="G93" s="560" t="n">
+        <v>26520</v>
+      </c>
+      <c r="H93" s="558" t="n">
+        <v>15888</v>
+      </c>
+      <c r="I93" s="608" t="n">
+        <v>10632</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="604" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+      <c r="B94" s="559" t="n">
+        <v>307919</v>
+      </c>
+      <c r="C94" s="559" t="n">
+        <v>310402</v>
+      </c>
+      <c r="D94" s="559" t="n">
+        <v>33039</v>
+      </c>
+      <c r="E94" s="559" t="n">
+        <v>277363</v>
+      </c>
+      <c r="F94" s="559" t="n">
+        <v>12</v>
+      </c>
+      <c r="G94" s="605" t="n">
+        <v>25660</v>
+      </c>
+      <c r="H94" s="559" t="n">
+        <v>23114</v>
+      </c>
+      <c r="I94" s="606" t="n">
+        <v>2546</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="185">
